--- a/generated/students_enriched.xlsx
+++ b/generated/students_enriched.xlsx
@@ -1,87 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
-  <si>
-    <t>student_name</t>
-  </si>
-  <si>
-    <t>department</t>
-  </si>
-  <si>
-    <t>thesis_title</t>
-  </si>
-  <si>
-    <t>research_fields</t>
-  </si>
-  <si>
-    <t>research_fields_text</t>
-  </si>
-  <si>
-    <t>佐藤健</t>
-  </si>
-  <si>
-    <t>田中葵</t>
-  </si>
-  <si>
-    <t>社会工学学位プログラム</t>
-  </si>
-  <si>
-    <t>都市交通需要予測に対する時系列深層学習の適用</t>
-  </si>
-  <si>
-    <t>災害時避難行動データを用いた最適配置モデルの研究</t>
-  </si>
-  <si>
-    <t>時系列解析 ; 交通工学 ; プログラム解析 ; 需要予測</t>
-  </si>
-  <si>
-    <t>防災 ; 最適化 ; プログラム解析 ; 社会ネットワーク分析</t>
-  </si>
-  <si>
-    <t>時系列解析 / 交通工学 / プログラム解析 / 需要予測</t>
-  </si>
-  <si>
-    <t>防災 / 最適化 / プログラム解析 / 社会ネットワーク分析</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -96,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -412,62 +420,617 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>student_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>thesis_title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>research_fields</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>research_fields_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>但木 陸</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>大学入試業務の人員配置最適化における数理モデルの改良</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>数理最適化 ; 組合せ最適化 ; 学習分析 ; 計算社会科学 ; 最適化</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>数理最適化 / 組合せ最適化 / 学習分析 / 計算社会科学 / 最適化</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>吉田 響</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>社会工学・サービス工学学位プログラムにおける修士論文審査員の割り当て問題</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>経営工学 ; 環境工学 ; 社会ネットワーク分析 ; ソフトウェア工学 ; 制御工学</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>経営工学 / 環境工学 / 社会ネットワーク分析 / ソフトウェア工学 / 制御工学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>金原 壮汰</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LiDARデータに基づく視線および姿勢情報統合による危険行動の動的検出システム〜荷役作業ケース</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>災害分析 ; 情報可視化 ; 機械学習 ; 画像処理 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>災害分析 / 情報可視化 / 機械学習 / 画像処理 / 学習分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>宍戸 唯輝</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3階層サプライチェーンにおける協調的納期決定アルゴリズム</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>サプライチェーン ; 組合せ最適化 ; 推薦システム ; 物流最適化 ; 需要予測</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>サプライチェーン / 組合せ最適化 / 推薦システム / 物流最適化 / 需要予測</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>堤 敬信</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>閉鎖型待ち行列ネットワークモデルを用いたシェアサイクルの運用分析</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; ネットワーク科学 ; 分散システム ; 学習分析 ; サプライチェーン</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / ネットワーク科学 / 分散システム / 学習分析 / サプライチェーン</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>寺田 海渡</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>中小企業デフォルト予測における月次流動性預金残高特徴量の有効性検証</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>需要予測 ; 学習分析 ; マーケティング分析 ; 災害分析 ; 行政データ分析</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>需要予測 / 学習分析 / マーケティング分析 / 災害分析 / 行政データ分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>益子 颯太</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>仕訳データの異常検知モデルの高度化：Data Collaboration解析と摘要欄の活用</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>学習分析 ; 行政データ分析 ; センサデータ解析 ; 組合せ最適化 ; プログラム解析</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>学習分析 / 行政データ分析 / センサデータ解析 / 組合せ最適化 / プログラム解析</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>平井 佑樹</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>仕訳データを用いた利速測定の研究</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>センサデータ解析 ; 学習分析 ; 行政データ分析 ; 統計学 ; スポーツ科学</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>センサデータ解析 / 学習分析 / 行政データ分析 / 統計学 / スポーツ科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>飯田 真実</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HPVワクチン接種に対する意見の変遷とその要因</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>政策評価 ; 因果推論 ; プライバシー保護 ; 強化学習 ; 医用画像</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>政策評価 / 因果推論 / プライバシー保護 / 強化学習 / 医用画像</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>川井 貫太朗</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SNSを用いた労働者の集団感情分析</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; 学習分析 ; 災害分析 ; 計算社会科学 ; 意思決定支援</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / 学習分析 / 災害分析 / 計算社会科学 / 意思決定支援</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>冨樫 歩大</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>テキスト情報と財務情報の統合による中小企業の将来性予測</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>需要予測 ; 行政データ分析 ; 経営工学 ; 情報可視化 ; マーケティング分析</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>需要予測 / 行政データ分析 / 経営工学 / 情報可視化 / マーケティング分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>出口 達也</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>地域要因を用いた慢性腎臓病患者の悪化予測の研究</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>需要予測 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>需要予測 / 社会ネットワーク分析 / 行政データ分析 / 災害分析 / 学習分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>長谷川 弘貴</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>生体情報とテンソルデータ解析によるコンサート満足度の研究</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>センサデータ解析 ; 行政データ分析 ; 観光情報学 ; 社会ネットワーク分析 ; 情報検索</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>センサデータ解析 / 行政データ分析 / 観光情報学 / 社会ネットワーク分析 / 情報検索</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>中山 友琉</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>特異値分解を用いた効率的な分散データファインチューニング手法の提案</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>分散システム ; センサデータ解析 ; 組合せ最適化 ; 数理最適化 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>分散システム / センサデータ解析 / 組合せ最適化 / 数理最適化 / 学習分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>齋藤 彩</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>地域愛着の規定因に関する実証分析：つながりの影響の検討</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; 政策評価 ; 因果推論 ; 行政データ分析 ; ネットワーク科学</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 / 政策評価 / 因果推論 / 行政データ分析 / ネットワーク科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>李 宗晟</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>エラスティック光ネットワークにおける通信要求の保持時間を考慮した予約種別リソース割り当て戦略の提案</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>推薦システム ; ネットワーク科学 ; 需要予測 ; 分散システム ; 物流最適化</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>推薦システム / ネットワーク科学 / 需要予測 / 分散システム / 物流最適化</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>澤口 瑛都</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>列生成法を軸とした電気バスの仕業編成最適化</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>組合せ最適化 ; 物流最適化 ; 数理最適化 ; 最適化 ; 推薦システム</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>組合せ最適化 / 物流最適化 / 数理最適化 / 最適化 / 推薦システム</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>中本 武志</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>大規模言語モデルを活用した非専門家による継続運用可能な勤務表作成手法の検討</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>大規模言語モデル ; 学習分析 ; 自然言語処理 ; 行政データ分析 ; 機械学習</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>大規模言語モデル / 学習分析 / 自然言語処理 / 行政データ分析 / 機械学習</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>髙橋 優介</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>重量・近接規制を考慮した異種ドローン経路問題：規制による配送時間・コストへの影響分析</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>物流最適化 ; マーケティング分析 ; 災害分析 ; サプライチェーン ; 学習分析</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>物流最適化 / マーケティング分析 / 災害分析 / サプライチェーン / 学習分析</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>鈴木 颯斗</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>最適多分木を用いた解釈可能なクラスタリング</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>数理最適化 ; 組合せ最適化 ; 学習分析 ; プログラム解析 ; 最適化</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>数理最適化 / 組合せ最適化 / 学習分析 / プログラム解析 / 最適化</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>佐川 翼</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>社会工学・サービス工学学位プログラムにおける修士論文発表会スケジューリングシステムの開発</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ソフトウェア工学 ; 社会ネットワーク分析 ; 計算社会科学 ; 環境工学 ; 経営工学</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ソフトウェア工学 / 社会ネットワーク分析 / 計算社会科学 / 環境工学 / 経営工学</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>加田 昌杜</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>学年暦の自動生成 〜曜日変更最小化モデルとその修正の自動化〜</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>学習分析 ; 数理最適化 ; 機械学習 ; 最適化 ; 組合せ最適化</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>学習分析 / 数理最適化 / 機械学習 / 最適化 / 組合せ最適化</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>八角 朋樹</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>機械学習モデルと特徴量選択によるファミリーレストラン店舗別売上予測方法の検討</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>学習分析 ; 機械学習 ; マーケティング分析 ; 需要予測 ; 組合せ最適化</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>学習分析 / 機械学習 / マーケティング分析 / 需要予測 / 組合せ最適化</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>山下 穂乃花</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Continual Learning by Null Space of Weight Matrix of Previous Task for Deep Neural Network</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>深層学習 ; 学習分析 ; 機械学習 ; 強化学習 ; 数理最適化</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>深層学習 / 学習分析 / 機械学習 / 強化学習 / 数理最適化</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>崔 涵喬</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>観光客のセグメンテーションとマーケティングへの応用可能性に関する研究</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>観光情報学 ; マーケティング分析 ; 政策評価 ; 社会ネットワーク分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>観光情報学 / マーケティング分析 / 政策評価 / 社会ネットワーク分析 / 学習分析</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/generated/students_enriched.xlsx
+++ b/generated/students_enriched.xlsx
@@ -469,12 +469,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; 学習分析 ; 計算社会科学 ; 最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; 最適化</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>数理最適化 / 組合せ最適化 / 学習分析 / 計算社会科学 / 最適化</t>
+          <t>数理最適化 / 組合せ最適化 / 最適化</t>
         </is>
       </c>
     </row>
@@ -492,12 +492,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>経営工学 ; 環境工学 ; 社会ネットワーク分析 ; ソフトウェア工学 ; 制御工学</t>
+          <t>経営工学 ; 社会ネットワーク分析 ; ソフトウェア工学</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>経営工学 / 環境工学 / 社会ネットワーク分析 / ソフトウェア工学 / 制御工学</t>
+          <t>経営工学 / 社会ネットワーク分析 / ソフトウェア工学</t>
         </is>
       </c>
     </row>
@@ -515,12 +515,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>災害分析 ; 情報可視化 ; 機械学習 ; 画像処理 ; 学習分析</t>
+          <t>災害分析 ; 情報可視化 ; 信号処理</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>災害分析 / 情報可視化 / 機械学習 / 画像処理 / 学習分析</t>
+          <t>災害分析 / 情報可視化 / 信号処理</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>サプライチェーン ; 組合せ最適化 ; 推薦システム ; 物流最適化 ; 需要予測</t>
+          <t>サプライチェーン ; 推薦システム ; 組合せ最適化</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>サプライチェーン / 組合せ最適化 / 推薦システム / 物流最適化 / 需要予測</t>
+          <t>サプライチェーン / 推薦システム / 組合せ最適化</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>社会ネットワーク分析 ; ネットワーク科学 ; 分散システム ; 学習分析 ; サプライチェーン</t>
+          <t>社会ネットワーク分析 ; ネットワーク科学 ; 分散システム</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>社会ネットワーク分析 / ネットワーク科学 / 分散システム / 学習分析 / サプライチェーン</t>
+          <t>社会ネットワーク分析 / ネットワーク科学 / 分散システム</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>需要予測 ; 学習分析 ; マーケティング分析 ; 災害分析 ; 行政データ分析</t>
+          <t>需要予測 ; 学習分析 ; マーケティング分析</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>需要予測 / 学習分析 / マーケティング分析 / 災害分析 / 行政データ分析</t>
+          <t>需要予測 / 学習分析 / マーケティング分析</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>学習分析 ; 行政データ分析 ; センサデータ解析 ; 組合せ最適化 ; プログラム解析</t>
+          <t>センサデータ解析 ; 行政データ分析 ; 異常検知</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>学習分析 / 行政データ分析 / センサデータ解析 / 組合せ最適化 / プログラム解析</t>
+          <t>センサデータ解析 / 行政データ分析 / 異常検知</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>センサデータ解析 ; 学習分析 ; 行政データ分析 ; 統計学 ; スポーツ科学</t>
+          <t>センサデータ解析 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>センサデータ解析 / 学習分析 / 行政データ分析 / 統計学 / スポーツ科学</t>
+          <t>センサデータ解析 / 行政データ分析 / 学習分析</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>政策評価 ; 因果推論 ; プライバシー保護 ; 強化学習 ; 医用画像</t>
+          <t>政策評価 ; プライバシー保護 ; 因果推論</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>政策評価 / 因果推論 / プライバシー保護 / 強化学習 / 医用画像</t>
+          <t>政策評価 / プライバシー保護 / 因果推論</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>社会ネットワーク分析 ; 学習分析 ; 災害分析 ; 計算社会科学 ; 意思決定支援</t>
+          <t>社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>社会ネットワーク分析 / 学習分析 / 災害分析 / 計算社会科学 / 意思決定支援</t>
+          <t>社会ネットワーク分析 / 行政データ分析 / 学習分析</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>需要予測 ; 行政データ分析 ; 経営工学 ; 情報可視化 ; マーケティング分析</t>
+          <t>需要予測 ; 行政データ分析 ; 情報可視化</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>需要予測 / 行政データ分析 / 経営工学 / 情報可視化 / マーケティング分析</t>
+          <t>需要予測 / 行政データ分析 / 情報可視化</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>需要予測 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析 ; 学習分析</t>
+          <t>需要予測 ; 社会ネットワーク分析 ; 行政データ分析</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>需要予測 / 社会ネットワーク分析 / 行政データ分析 / 災害分析 / 学習分析</t>
+          <t>需要予測 / 社会ネットワーク分析 / 行政データ分析</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>センサデータ解析 ; 行政データ分析 ; 観光情報学 ; 社会ネットワーク分析 ; 情報検索</t>
+          <t>センサデータ解析 ; 行政データ分析 ; 観光情報学</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>センサデータ解析 / 行政データ分析 / 観光情報学 / 社会ネットワーク分析 / 情報検索</t>
+          <t>センサデータ解析 / 行政データ分析 / 観光情報学</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>分散システム ; センサデータ解析 ; 組合せ最適化 ; 数理最適化 ; 学習分析</t>
+          <t>分散システム ; センサデータ解析 ; 組合せ最適化</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>分散システム / センサデータ解析 / 組合せ最適化 / 数理最適化 / 学習分析</t>
+          <t>分散システム / センサデータ解析 / 組合せ最適化</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>社会ネットワーク分析 ; 政策評価 ; 因果推論 ; 行政データ分析 ; ネットワーク科学</t>
+          <t>社会ネットワーク分析 ; 政策評価 ; 行政データ分析</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>社会ネットワーク分析 / 政策評価 / 因果推論 / 行政データ分析 / ネットワーク科学</t>
+          <t>社会ネットワーク分析 / 政策評価 / 行政データ分析</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>推薦システム ; ネットワーク科学 ; 需要予測 ; 分散システム ; 物流最適化</t>
+          <t>推薦システム ; 需要予測 ; ネットワーク科学</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>推薦システム / ネットワーク科学 / 需要予測 / 分散システム / 物流最適化</t>
+          <t>推薦システム / 需要予測 / ネットワーク科学</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>組合せ最適化 ; 物流最適化 ; 数理最適化 ; 最適化 ; 推薦システム</t>
+          <t>組合せ最適化 ; 物流最適化 ; 最適化</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>組合せ最適化 / 物流最適化 / 数理最適化 / 最適化 / 推薦システム</t>
+          <t>組合せ最適化 / 物流最適化 / 最適化</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>大規模言語モデル ; 学習分析 ; 自然言語処理 ; 行政データ分析 ; 機械学習</t>
+          <t>大規模言語モデル ; 学習分析 ; 行政データ分析</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>大規模言語モデル / 学習分析 / 自然言語処理 / 行政データ分析 / 機械学習</t>
+          <t>大規模言語モデル / 学習分析 / 行政データ分析</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>物流最適化 ; マーケティング分析 ; 災害分析 ; サプライチェーン ; 学習分析</t>
+          <t>物流最適化 ; 災害分析 ; マーケティング分析</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>物流最適化 / マーケティング分析 / 災害分析 / サプライチェーン / 学習分析</t>
+          <t>物流最適化 / 災害分析 / マーケティング分析</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; 学習分析 ; プログラム解析 ; 最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; 最適化</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>数理最適化 / 組合せ最適化 / 学習分析 / プログラム解析 / 最適化</t>
+          <t>数理最適化 / 組合せ最適化 / 最適化</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ソフトウェア工学 ; 社会ネットワーク分析 ; 計算社会科学 ; 環境工学 ; 経営工学</t>
+          <t>ソフトウェア工学 ; 社会ネットワーク分析 ; 計算社会科学</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ソフトウェア工学 / 社会ネットワーク分析 / 計算社会科学 / 環境工学 / 経営工学</t>
+          <t>ソフトウェア工学 / 社会ネットワーク分析 / 計算社会科学</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>学習分析 ; 数理最適化 ; 機械学習 ; 最適化 ; 組合せ最適化</t>
+          <t>数理最適化 ; 学習分析 ; 最適化</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>学習分析 / 数理最適化 / 機械学習 / 最適化 / 組合せ最適化</t>
+          <t>数理最適化 / 学習分析 / 最適化</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>学習分析 ; 機械学習 ; マーケティング分析 ; 需要予測 ; 組合せ最適化</t>
+          <t>学習分析 ; 機械学習 ; マーケティング分析</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>学習分析 / 機械学習 / マーケティング分析 / 需要予測 / 組合せ最適化</t>
+          <t>学習分析 / 機械学習 / マーケティング分析</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>深層学習 ; 学習分析 ; 機械学習 ; 強化学習 ; 数理最適化</t>
+          <t>深層学習 ; 学習分析 ; 機械学習</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>深層学習 / 学習分析 / 機械学習 / 強化学習 / 数理最適化</t>
+          <t>深層学習 / 学習分析 / 機械学習</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>観光情報学 ; マーケティング分析 ; 政策評価 ; 社会ネットワーク分析 ; 学習分析</t>
+          <t>観光情報学 ; マーケティング分析 ; 政策評価</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>観光情報学 / マーケティング分析 / 政策評価 / 社会ネットワーク分析 / 学習分析</t>
+          <t>観光情報学 / マーケティング分析 / 政策評価</t>
         </is>
       </c>
     </row>

--- a/generated/students_enriched.xlsx
+++ b/generated/students_enriched.xlsx
@@ -497,26 +497,21 @@
           <t>経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>nan ; 労働経済・就職マッチング ; 意思決定分析 ; 機械学習</t>
+          <t>経済モデリング ; 意思決定分析 ; 労働経済・就職マッチング ; 機械学習</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; マーケティング分析 ; 学習分析</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>経済モデリング
 意思決定分析
-nan
 労働経済・就職マッチング
 機械学習
 労働経済
@@ -529,13 +524,14 @@
 意思決定支援
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+マーケティング分析
+学習分析</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>日本の就活市場における新卒採用に関する研究
-nan</t>
+          <t>日本の就活市場における新卒採用に関する研究</t>
         </is>
       </c>
     </row>
@@ -560,26 +556,21 @@
           <t>経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>nan ; 家族・人口政策 ; 意思決定分析 ; 機械学習 ; 政策評価・計量分析</t>
+          <t>経済モデリング ; 意思決定分析 ; 家族・人口政策 ; 機械学習 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; マーケティング分析</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>経済モデリング
 意思決定分析
-nan
 家族・人口政策
 機械学習
 政策評価・計量分析
@@ -597,13 +588,13 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+マーケティング分析</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>結婚の意思決定に対する独身税の効果と税制度の提案
-nan</t>
+          <t>結婚の意思決定に対する独身税の効果と税制度の提案</t>
         </is>
       </c>
     </row>
@@ -628,26 +619,21 @@
           <t>経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nan ; 労働経済・就職マッチング ; 意思決定分析 ; 機械学習</t>
+          <t>経済モデリング ; 意思決定分析 ; 労働経済・就職マッチング ; 機械学習</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 学習分析 ; マーケティング分析</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>経済モデリング
 意思決定分析
-nan
 労働経済・就職マッチング
 機械学習
 労働経済
@@ -660,13 +646,14 @@
 意思決定支援
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+学習分析
+マーケティング分析</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>学生の選考情報を利用した就活支援サービスに関する研究
-nan</t>
+          <t>学生の選考情報を利用した就活支援サービスに関する研究</t>
         </is>
       </c>
     </row>
@@ -691,19 +678,15 @@
           <t>数理最適化 ; 組合せ最適化 ; 経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nan ; 労働経済・就職マッチング ; 意思決定分析 ; オペレーションズリサーチ ; 機械学習</t>
+          <t>数理最適化 ; 組合せ最適化 ; 経済モデリング ; 意思決定分析 ; 労働経済・就職マッチング ; オペレーションズリサーチ ; 機械学習</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; マーケティング分析</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -712,7 +695,6 @@
 組合せ最適化
 経済モデリング
 意思決定分析
-nan
 労働経済・就職マッチング
 オペレーションズリサーチ
 機械学習
@@ -727,13 +709,13 @@
 計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+マーケティング分析</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>最適停止問題を用いた就活市場の分析と改善提案
-nan</t>
+          <t>最適停止問題を用いた就活市場の分析と改善提案</t>
         </is>
       </c>
     </row>
@@ -758,26 +740,21 @@
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nan ; 保険・金融行動 ; 画像・視覚情報処理</t>
+          <t>行動科学 ; 行動経済学 ; 保険・金融行動 ; 画像・視覚情報処理</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 行動科学 ; 学習分析 ; マーケティング分析</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
-nan
 保険・金融行動
 画像・視覚情報処理
 行動ファイナンス
@@ -787,13 +764,14 @@
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析</t>
+マルチモーダル解析
+学習分析
+マーケティング分析</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>視線計測を用いた保険加入行動の分析
-nan</t>
+          <t>視線計測を用いた保険加入行動の分析</t>
         </is>
       </c>
     </row>
@@ -818,26 +796,21 @@
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>nan ; 意思決定分析 ; 政策評価・計量分析</t>
+          <t>行動科学 ; 行動経済学 ; 意思決定分析 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行動科学 ; 経営工学</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
-nan
 意思決定分析
 政策評価・計量分析
 行動意思決定
@@ -847,13 +820,13 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+経営工学</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>価値観が失敗の対処行動に与える影響-失敗体験の重大性と領域を考えて-
-nan</t>
+          <t>価値観が失敗の対処行動に与える影響-失敗体験の重大性と領域を考えて-</t>
         </is>
       </c>
     </row>
@@ -878,37 +851,34 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nan ; マッチング理論・ゲーム理論</t>
+          <t>データ分析 ; 社会システム分析 ; マッチング理論・ゲーム理論</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム</t>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 社会ネットワーク分析 ; 行政データ分析 ; 計算社会科学</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 マッチング理論・ゲーム理論
 安定マッチング
 資源配分
 メカニズムデザイン
-協力ゲーム・非協力ゲーム</t>
+協力ゲーム・非協力ゲーム
+社会ネットワーク分析
+行政データ分析
+計算社会科学</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Priority-neutral matchingsの集合の格子構造に関する研究
-nan</t>
+          <t>Priority-neutral matchingsの集合の格子構造に関する研究</t>
         </is>
       </c>
     </row>
@@ -933,19 +903,15 @@
           <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nan ; マッチング理論・ゲーム理論 ; オペレーションズリサーチ ; 機械学習</t>
+          <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化 ; マッチング理論・ゲーム理論 ; オペレーションズリサーチ ; 機械学習</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 最適化</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -954,7 +920,6 @@
 組合せ最適化
 確率モデリング
 確率最適化
-nan
 マッチング理論・ゲーム理論
 オペレーションズリサーチ
 機械学習
@@ -965,13 +930,13 @@
 計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+最適化</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>不確実性下の同質財割当における randomized uniform rule のパレート効率性について
-nan</t>
+          <t>不確実性下の同質財割当における randomized uniform rule のパレート効率性について</t>
         </is>
       </c>
     </row>
@@ -996,25 +961,20 @@
           <t>マルチエージェントシミュレーション</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; GIS・空間分析 ; 政策評価・計量分析</t>
+          <t>マルチエージェントシミュレーション ; 都市・地域政策 ; GIS・空間分析 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 行政データ分析 ; シミュレーション</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>マルチエージェントシミュレーション
-nan
 都市・地域政策
 GIS・空間分析
 政策評価・計量分析
@@ -1029,13 +989,15 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+社会ネットワーク分析
+行政データ分析
+シミュレーション</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>都市特性・社会経済要因が外国人居住パターンに与える影響：東京23区の実証・シミュレーション分析
-nan</t>
+          <t>都市特性・社会経済要因が外国人居住パターンに与える影響：東京23区の実証・シミュレーション分析</t>
         </is>
       </c>
     </row>
@@ -1060,19 +1022,15 @@
           <t>数理最適化 ; 組合せ最適化 ; マルチエージェントシミュレーション</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ ; 建築・空間設計</t>
+          <t>数理最適化 ; 組合せ最適化 ; マルチエージェントシミュレーション ; オペレーションズリサーチ ; 建築・空間設計</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 最適化</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1080,20 +1038,19 @@
           <t>数理最適化
 組合せ最適化
 マルチエージェントシミュレーション
-nan
 オペレーションズリサーチ
 建築・空間設計
 計画・スケジューリング
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン</t>
+都市空間デザイン
+最適化</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>マルチエージェントシミュレーション&amp;最適化による間取り生成
-nan</t>
+          <t>マルチエージェントシミュレーション&amp;最適化による間取り生成</t>
         </is>
       </c>
     </row>
@@ -1118,36 +1075,33 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>nan ; スポーツデータ分析</t>
+          <t>データ分析 ; 社会システム分析 ; スポーツデータ分析</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析</t>
+          <t>スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 スポーツデータ分析
 スポーツアナリティクス
 戦術分析
-パフォーマンス分析</t>
+パフォーマンス分析
+社会ネットワーク分析
+行政データ分析
+学習分析</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>eスポーツにおけるチームのプレイスタイル分析
-nan</t>
+          <t>eスポーツにおけるチームのプレイスタイル分析</t>
         </is>
       </c>
     </row>
@@ -1172,36 +1126,32 @@
           <t>ネットワーク科学 ; グラフ理論</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>nan ; ネットワーク・グラフ理論</t>
+          <t>ネットワーク科学 ; グラフ理論 ; ネットワーク・グラフ理論</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
+          <t>グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; ネットワーク科学 ; 知識グラフ ; 数理モデリング</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>ネットワーク科学
 グラフ理論
-nan
 ネットワーク・グラフ理論
 離散数学
 ネットワーク最適化
-組合せ構造</t>
+組合せ構造
+知識グラフ
+数理モデリング</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>単位コイングラフにおける部分彩色の拡張
-nan</t>
+          <t>単位コイングラフにおける部分彩色の拡張</t>
         </is>
       </c>
     </row>
@@ -1226,19 +1176,15 @@
           <t>数理最適化 ; 組合せ最適化 ; ネットワーク科学 ; グラフ理論 ; 交通工学 ; 輸送最適化</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>nan ; 家族・人口政策 ; オペレーションズリサーチ ; 交通・モビリティ ; ネットワーク・グラフ理論</t>
+          <t>数理最適化 ; 組合せ最適化 ; ネットワーク科学 ; グラフ理論 ; 交通工学 ; 輸送最適化 ; 家族・人口政策 ; オペレーションズリサーチ ; 交通・モビリティ ; ネットワーク・グラフ理論</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; ネットワーク科学</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1249,7 +1195,6 @@
 グラフ理論
 交通工学
 輸送最適化
-nan
 家族・人口政策
 オペレーションズリサーチ
 交通・モビリティ
@@ -1269,8 +1214,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>人口を考慮した均等輸送問題による道路ネットワークの連結性の定量化とその最適補強問題
-nan</t>
+          <t>人口を考慮した均等輸送問題による道路ネットワークの連結性の定量化とその最適補強問題</t>
         </is>
       </c>
     </row>
@@ -1295,19 +1239,15 @@
           <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化 ; 交通工学 ; 輸送最適化 ; エネルギーシステム ; 運用最適化</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ ; 交通・モビリティ ; 機械学習</t>
+          <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化 ; 交通工学 ; 輸送最適化 ; エネルギーシステム ; 運用最適化 ; オペレーションズリサーチ ; 交通・モビリティ ; 機械学習 ; 環境・エネルギー</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 最適化</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1320,23 +1260,26 @@
 輸送最適化
 エネルギーシステム
 運用最適化
-nan
 オペレーションズリサーチ
 交通・モビリティ
 機械学習
+環境・エネルギー
 計画・スケジューリング
 モビリティ設計
 交通需要分析
 ネットワーク設計
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+環境政策
+脱炭素分析
+持続可能性評価
+最適化</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>消費電力と所要時間の不確実性を考慮した電動バスの運行計画最適化
-nan</t>
+          <t>消費電力と所要時間の不確実性を考慮した電動バスの運行計画最適化</t>
         </is>
       </c>
     </row>
@@ -1361,34 +1304,29 @@
           <t>数理最適化 ; 組合せ最適化</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 物流最適化</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>数理最適化
 組合せ最適化
-nan
 オペレーションズリサーチ
-計画・スケジューリング</t>
+計画・スケジューリング
+物流最適化</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>品質保証時間と工場間搬送を考慮した多目的マルチファクトリー・スケジューリング
-nan</t>
+          <t>品質保証時間と工場間搬送を考慮した多目的マルチファクトリー・スケジューリング</t>
         </is>
       </c>
     </row>
@@ -1413,37 +1351,33 @@
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>nan ; 意思決定分析</t>
+          <t>行動科学 ; 行動経済学 ; 意思決定分析</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援</t>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 行動科学 ; 学習分析 ; 最適化</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
-nan
 意思決定分析
 行動意思決定
 実験・行動分析
 ナッジ
-意思決定支援</t>
+意思決定支援
+学習分析
+最適化</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>自律性モデルに基づくゲーミフィケーションによる安全行動変容
-nan</t>
+          <t>自律性モデルに基づくゲーミフィケーションによる安全行動変容</t>
         </is>
       </c>
     </row>
@@ -1468,19 +1402,15 @@
           <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化 ; データサイエンス ; 統計モデリング</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ ; 機械学習</t>
+          <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化 ; データサイエンス ; 統計モデリング ; オペレーションズリサーチ ; 機械学習</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 最適化</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1491,19 +1421,18 @@
 確率最適化
 データサイエンス
 統計モデリング
-nan
 オペレーションズリサーチ
 機械学習
 計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+最適化</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>確率的最適化による高次元交互作用スパースモデリング~Factorization Machines の発展形態
-nan</t>
+          <t>確率的最適化による高次元交互作用スパースモデリング~Factorization Machines の発展形態</t>
         </is>
       </c>
     </row>
@@ -1528,41 +1457,43 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>nan ; 機械学習 ; 画像・視覚情報処理</t>
+          <t>データ分析 ; 社会システム分析 ; 機械学習 ; 画像・視覚情報処理 ; 医療・ヘルスデータ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 行政データ分析 ; 社会ネットワーク分析 ; センサデータ解析</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 機械学習
 画像・視覚情報処理
+医療・ヘルスデータ
 統計的学習
 予測モデリング
 表現学習
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析</t>
+マルチモーダル解析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+行政データ分析
+社会ネットワーク分析
+センサデータ解析</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>画像と生体計測情報に基づくアクティブラーニングと業務管理
-nan</t>
+          <t>画像と生体計測情報に基づくアクティブラーニングと業務管理</t>
         </is>
       </c>
     </row>
@@ -1587,26 +1518,21 @@
           <t>ゲーム理論 ; マッチング理論</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>nan ; マッチング理論・ゲーム理論 ; 交通・モビリティ</t>
+          <t>ゲーム理論 ; マッチング理論 ; マッチング理論・ゲーム理論 ; 交通・モビリティ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 学習分析 ; マーケティング分析 ; 組合せ最適化</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>ゲーム理論
 マッチング理論
-nan
 マッチング理論・ゲーム理論
 交通・モビリティ
 安定マッチング
@@ -1616,13 +1542,15 @@
 交通工学
 モビリティ設計
 交通需要分析
-ネットワーク設計</t>
+ネットワーク設計
+学習分析
+マーケティング分析
+組合せ最適化</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>単独と集団を区別したライドシェアモデルにおけるゲーム理論的解析
-nan</t>
+          <t>単独と集団を区別したライドシェアモデルにおけるゲーム理論的解析</t>
         </is>
       </c>
     </row>
@@ -1647,36 +1575,33 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ</t>
+          <t>データ分析 ; 社会システム分析 ; オペレーションズリサーチ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 分散システム ; 社会ネットワーク分析 ; 行政データ分析</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 オペレーションズリサーチ
 数理最適化
 組合せ最適化
-計画・スケジューリング</t>
+計画・スケジューリング
+分散システム
+社会ネットワーク分析
+行政データ分析</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>異なる容量を持つ複数システムの負荷分散
-nan</t>
+          <t>異なる容量を持つ複数システムの負荷分散</t>
         </is>
       </c>
     </row>
@@ -1701,26 +1626,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>nan ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計</t>
+          <t>データ分析 ; 社会システム分析 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 GIS・空間分析
 交通・モビリティ
 建築・空間設計
@@ -1735,13 +1655,15 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン</t>
+都市空間デザイン
+社会ネットワーク分析
+行政データ分析
+学習分析</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>歩車共存空間における歩行者の移動モデルの構築
-nan</t>
+          <t>歩車共存空間における歩行者の移動モデルの構築</t>
         </is>
       </c>
     </row>
@@ -1766,26 +1688,21 @@
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>nan ; 機械学習 ; 画像・視覚情報処理</t>
+          <t>行動科学 ; 行動経済学 ; 機械学習 ; 画像・視覚情報処理</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 行動科学 ; 学習分析 ; 認知科学</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
-nan
 機械学習
 画像・視覚情報処理
 統計的学習
@@ -1794,13 +1711,14 @@
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析</t>
+マルチモーダル解析
+学習分析
+認知科学</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>骨格に基づく行動認識における関節角の導入
-nan</t>
+          <t>骨格に基づく行動認識における関節角の導入</t>
         </is>
       </c>
     </row>
@@ -1825,26 +1743,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>nan ; 労働経済・就職マッチング ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 労働経済・就職マッチング ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 計算社会科学</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 労働経済・就職マッチング
 政策評価・計量分析
 労働経済
@@ -1854,13 +1767,15 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+行政データ分析
+社会ネットワーク分析
+計算社会科学</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>日本における男女の賃金格差の推移
-nan</t>
+          <t>日本における男女の賃金格差の推移</t>
         </is>
       </c>
     </row>
@@ -1885,41 +1800,43 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>nan ; 保険・金融行動 ; 機械学習</t>
+          <t>データ分析 ; 社会システム分析 ; 保険・金融行動 ; 機械学習 ; テキスト分析・NLP</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 社会ネットワーク分析 ; 行政データ分析 ; センサデータ解析</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 保険・金融行動
 機械学習
+テキスト分析・NLP
 行動ファイナンス
 金融市場分析
 ESG投資
 企業財務
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+テキストマイニング
+自然言語処理
+感情分析
+社会データ分析
+社会ネットワーク分析
+行政データ分析
+センサデータ解析</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SNS上のESGセンチメント
-nan</t>
+          <t>SNS上のESGセンチメント</t>
         </is>
       </c>
     </row>
@@ -1944,26 +1861,21 @@
           <t>経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>nan ; 保険・金融行動 ; 意思決定分析 ; 機械学習</t>
+          <t>経済モデリング ; 意思決定分析 ; 保険・金融行動 ; 機械学習</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; マーケティング分析 ; 学習分析</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>経済モデリング
 意思決定分析
-nan
 保険・金融行動
 機械学習
 行動ファイナンス
@@ -1976,13 +1888,14 @@
 意思決定支援
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+マーケティング分析
+学習分析</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ESG関連インデックスと株式市場
-nan</t>
+          <t>ESG関連インデックスと株式市場</t>
         </is>
       </c>
     </row>
@@ -2007,26 +1920,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>nan ; 労働経済・就職マッチング ; 社会政策・福祉 ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 労働経済・就職マッチング ; 社会政策・福祉 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 学習分析</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 労働経済・就職マッチング
 社会政策・福祉
 政策評価・計量分析
@@ -2041,13 +1949,15 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+行政データ分析
+社会ネットワーク分析
+学習分析</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>介護が労働に与える影響
-nan</t>
+          <t>介護が労働に与える影響</t>
         </is>
       </c>
     </row>
@@ -2072,34 +1982,29 @@
           <t>数理最適化 ; 組合せ最適化</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 物流最適化</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>数理最適化
 組合せ最適化
-nan
 オペレーションズリサーチ
-計画・スケジューリング</t>
+計画・スケジューリング
+物流最適化</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>複数工場間の経路最適化を含む多目的マルチファクトリー・スケジューリング
-nan</t>
+          <t>複数工場間の経路最適化を含む多目的マルチファクトリー・スケジューリング</t>
         </is>
       </c>
     </row>
@@ -2124,26 +2029,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>nan ; 機械学習 ; 画像・視覚情報処理</t>
+          <t>データ分析 ; 社会システム分析 ; 機械学習 ; 画像・視覚情報処理</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 社会ネットワーク分析 ; 行政データ分析 ; 異常検知</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 機械学習
 画像・視覚情報処理
 統計的学習
@@ -2152,13 +2052,15 @@
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析</t>
+マルチモーダル解析
+社会ネットワーク分析
+行政データ分析
+異常検知</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>品質検査レイヤーを横断した異常原因探索～画像マルチモーダルアプローチ
-nan</t>
+          <t>品質検査レイヤーを横断した異常原因探索～画像マルチモーダルアプローチ</t>
         </is>
       </c>
     </row>
@@ -2183,36 +2085,33 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>nan ; サービス・待ち行列</t>
+          <t>データ分析 ; 社会システム分析 ; サービス・待ち行列</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>待ち行列理論 ; サービス工学 ; システム性能評価</t>
+          <t>待ち行列理論 ; サービス工学 ; システム性能評価 ; 社会ネットワーク分析 ; 行政データ分析 ; 推薦システム</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 サービス・待ち行列
 待ち行列理論
 サービス工学
-システム性能評価</t>
+システム性能評価
+社会ネットワーク分析
+行政データ分析
+推薦システム</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>機械サーバと人間サーバが混在するサービスシステムの性能解析
-nan</t>
+          <t>機械サーバと人間サーバが混在するサービスシステムの性能解析</t>
         </is>
       </c>
     </row>
@@ -2237,26 +2136,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>nan ; 保険・金融行動 ; 都市・地域政策 ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 保険・金融行動 ; 都市・地域政策 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; マーケティング分析</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 保険・金融行動
 都市・地域政策
 政策評価・計量分析
@@ -2271,13 +2165,15 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+行政データ分析
+社会ネットワーク分析
+マーケティング分析</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>東京証券取引所によるPBR改善要請の影響は企業特性によって異なるか？
-nan</t>
+          <t>東京証券取引所によるPBR改善要請の影響は企業特性によって異なるか？</t>
         </is>
       </c>
     </row>
@@ -2302,36 +2198,33 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>nan ; 災害・防災研究</t>
+          <t>データ分析 ; 社会システム分析 ; 災害・防災研究</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>災害社会学 ; 防災政策 ; リスク評価</t>
+          <t>災害社会学 ; 防災政策 ; リスク評価 ; 災害分析 ; 行政データ分析 ; 社会ネットワーク分析</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 災害・防災研究
 災害社会学
 防災政策
-リスク評価</t>
+リスク評価
+災害分析
+行政データ分析
+社会ネットワーク分析</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>四川大震災についての地元住民の記憶とその変容—汶川県映秀鎮と北川県を比較して—
-nan</t>
+          <t>四川大震災についての地元住民の記憶とその変容—汶川県映秀鎮と北川県を比較して—</t>
         </is>
       </c>
     </row>
@@ -2356,26 +2249,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>nan ; 家族・人口政策 ; 社会政策・福祉</t>
+          <t>データ分析 ; 社会システム分析 ; 家族・人口政策 ; 社会政策・福祉</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 社会ネットワーク分析 ; 行政データ分析 ; 政策評価</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 家族・人口政策
 社会政策・福祉
 家族の経済学
@@ -2385,13 +2273,15 @@
 社会福祉政策
 地域福祉
 子育て支援
-非営利組織論</t>
+非営利組織論
+社会ネットワーク分析
+行政データ分析
+政策評価</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>多様な主体が関わる出産祝いによる産後家庭アウトリーチの実態と課題－横浜市戸塚区の認定NPO法人こまちぷらすのウェルカムベビープロジェクトに着目して－
-nan</t>
+          <t>多様な主体が関わる出産祝いによる産後家庭アウトリーチの実態と課題－横浜市戸塚区の認定NPO法人こまちぷらすのウェルカムベビープロジェクトに着目して－</t>
         </is>
       </c>
     </row>
@@ -2416,37 +2306,34 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>nan ; 社会政策・福祉</t>
+          <t>データ分析 ; 社会システム分析 ; 社会政策・福祉</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論</t>
+          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 社会ネットワーク分析 ; 行政データ分析 ; 計算社会科学</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 社会政策・福祉
 社会福祉政策
 地域福祉
 子育て支援
-非営利組織論</t>
+非営利組織論
+社会ネットワーク分析
+行政データ分析
+計算社会科学</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>カフェ型居場所の開設・運営プロセスにおける障壁と支援に関する研究－認定NPO法人こまちぷらすの講座に着目して－
-nan</t>
+          <t>カフェ型居場所の開設・運営プロセスにおける障壁と支援に関する研究－認定NPO法人こまちぷらすの講座に着目して－</t>
         </is>
       </c>
     </row>
@@ -2471,26 +2358,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; 建築・空間設計</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 建築・空間設計</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 建築・空間設計
 都市経済
@@ -2500,13 +2382,15 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン</t>
+都市空間デザイン
+行政データ分析
+社会ネットワーク分析
+災害分析</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>斜面住宅地の存続可能性に関する研究 －段差解消のための共有財の維持管理に着目して－
-nan</t>
+          <t>斜面住宅地の存続可能性に関する研究 －段差解消のための共有財の維持管理に着目して－</t>
         </is>
       </c>
     </row>
@@ -2531,26 +2415,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 農業情報学</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 政策評価・計量分析
 都市経済
@@ -2560,13 +2439,15 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+行政データ分析
+社会ネットワーク分析
+農業情報学</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>公園の農的利用の効果と課題に関する研究
-nan</t>
+          <t>公園の農的利用の効果と課題に関する研究</t>
         </is>
       </c>
     </row>
@@ -2591,26 +2472,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 学習分析</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 政策評価・計量分析
 都市経済
@@ -2620,13 +2496,15 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+行政データ分析
+社会ネットワーク分析
+学習分析</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>地方自治体における統計的因果推論に基づく政策分析の適用方法に関する研究
-nan</t>
+          <t>地方自治体における統計的因果推論に基づく政策分析の適用方法に関する研究</t>
         </is>
       </c>
     </row>
@@ -2651,37 +2529,34 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 推薦システム</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 都市経済
 地域政策
 土地利用
-公共政策評価</t>
+公共政策評価
+行政データ分析
+社会ネットワーク分析
+推薦システム</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>地域外の人材を対象とした逆指名による創業支援制度の運用実態と他地域展開の可能性に関する研究
-nan</t>
+          <t>地域外の人材を対象とした逆指名による創業支援制度の運用実態と他地域展開の可能性に関する研究</t>
         </is>
       </c>
     </row>
@@ -2706,26 +2581,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 GIS・空間分析
 建築・空間設計
@@ -2740,13 +2610,15 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン</t>
+都市空間デザイン
+行政データ分析
+社会ネットワーク分析
+災害分析</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>地籍調査の進捗に関する地理空間分析
-nan</t>
+          <t>地籍調査の進捗に関する地理空間分析</t>
         </is>
       </c>
     </row>
@@ -2771,26 +2643,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 GIS・空間分析
 交通・モビリティ
@@ -2810,13 +2677,15 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+行政データ分析
+社会ネットワーク分析
+災害分析</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>羽田空港新飛行経路の運用開始が東京都心の不動産価値に与えた影響に関する計量分析
-nan</t>
+          <t>羽田空港新飛行経路の運用開始が東京都心の不動産価値に与えた影響に関する計量分析</t>
         </is>
       </c>
     </row>
@@ -2841,26 +2710,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; GIS・空間分析 ; 災害・防災研究 ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; GIS・空間分析 ; 災害・防災研究 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 災害分析 ; 行政データ分析 ; 社会ネットワーク分析</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 GIS・空間分析
 災害・防災研究
@@ -2879,13 +2743,15 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+災害分析
+行政データ分析
+社会ネットワーク分析</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>マニラ都市圏における洪水リスクが不動産価格に与える影響の分析
-nan</t>
+          <t>マニラ都市圏における洪水リスクが不動産価格に与える影響の分析</t>
         </is>
       </c>
     </row>
@@ -2910,28 +2776,33 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>データ分析 ; 社会システム分析 ; 災害・防災研究</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>災害社会学 ; 防災政策 ; リスク評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan</t>
+災害・防災研究
+災害社会学
+防災政策
+リスク評価
+行政データ分析
+社会ネットワーク分析
+災害分析</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>冒険遊び場における犯罪被害と運営者の対応の実態解明
-nan</t>
+          <t>冒険遊び場における犯罪被害と運営者の対応の実態解明</t>
         </is>
       </c>
     </row>
@@ -2956,26 +2827,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>nan ; GIS・空間分析 ; 建築・空間設計</t>
+          <t>データ分析 ; 社会システム分析 ; GIS・空間分析 ; 建築・空間設計</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 GIS・空間分析
 建築・空間設計
 GIS
@@ -2985,13 +2851,15 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン</t>
+都市空間デザイン
+社会ネットワーク分析
+行政データ分析
+学習分析</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>屋外着座空間への評価と独り好き志向性との関係
-nan</t>
+          <t>屋外着座空間への評価と独り好き志向性との関係</t>
         </is>
       </c>
     </row>
@@ -3016,28 +2884,34 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>データ分析 ; 社会システム分析 ; 建築・空間設計</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 社会ネットワーク分析 ; 農業情報学 ; 行政データ分析</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan</t>
+建築・空間設計
+建築計画
+空間レイアウト生成
+居住空間設計
+都市空間デザイン
+社会ネットワーク分析
+農業情報学
+行政データ分析</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>農村舞台の現状とその保全—ハード・ソフトの両面に着目して—
-nan</t>
+          <t>農村舞台の現状とその保全—ハード・ソフトの両面に着目して—</t>
         </is>
       </c>
     </row>
@@ -3062,26 +2936,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 行政データ分析 ; 社会ネットワーク分析 ; 都市計画</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 GIS・空間分析
 建築・空間設計
@@ -3096,13 +2965,15 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン</t>
+都市空間デザイン
+行政データ分析
+社会ネットワーク分析
+都市計画</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ディープラーニングに基づく武漢の都市イメージの空間構造と都市計画実施に関する研究
-nan</t>
+          <t>ディープラーニングに基づく武漢の都市イメージの空間構造と都市計画実施に関する研究</t>
         </is>
       </c>
     </row>
@@ -3127,26 +2998,21 @@
           <t>ネットワーク科学 ; グラフ理論</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; ネットワーク・グラフ理論</t>
+          <t>ネットワーク科学 ; グラフ理論 ; 都市・地域政策 ; ネットワーク・グラフ理論</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 社会ネットワーク分析 ; ネットワーク科学 ; 行政データ分析</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>ネットワーク科学
 グラフ理論
-nan
 都市・地域政策
 ネットワーク・グラフ理論
 都市経済
@@ -3155,13 +3021,14 @@
 公共政策評価
 離散数学
 ネットワーク最適化
-組合せ構造</t>
+組合せ構造
+社会ネットワーク分析
+行政データ分析</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>地域ネットワークにおける中間支援組織の役割とマネジメントシステムの構築に関する考察
-nan</t>
+          <t>地域ネットワークにおける中間支援組織の役割とマネジメントシステムの構築に関する考察</t>
         </is>
       </c>
     </row>
@@ -3186,26 +3053,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 政策評価・計量分析
 都市経済
@@ -3215,13 +3077,15 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+行政データ分析
+社会ネットワーク分析
+災害分析</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>都市再生緊急整備地域における都市再生の政策効果の検証ー地方中核都市の事例を対象として
-nan</t>
+          <t>都市再生緊急整備地域における都市再生の政策効果の検証ー地方中核都市の事例を対象として</t>
         </is>
       </c>
     </row>
@@ -3246,28 +3110,24 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 政策評価・計量分析 ; 観光・マーケティング</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 行政データ分析 ; 社会ネットワーク分析 ; 観光情報学</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 政策評価・計量分析
+観光・マーケティング
 都市経済
 地域政策
 土地利用
@@ -3275,13 +3135,19 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+観光データ分析
+マーケティング分析
+クラスタリング
+需要予測
+行政データ分析
+社会ネットワーク分析
+観光情報学</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>観光都市におけるオーバーツーリズムの対策やそれに伴う効果と課題について
-nan</t>
+          <t>観光都市におけるオーバーツーリズムの対策やそれに伴う効果と課題について</t>
         </is>
       </c>
     </row>
@@ -3306,37 +3172,39 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>nan ; 建築・空間設計</t>
+          <t>データ分析 ; 社会システム分析 ; 建築・空間設計 ; 観光・マーケティング</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
+          <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 行政データ分析 ; 社会ネットワーク分析 ; 観光情報学</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 建築・空間設計
+観光・マーケティング
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン</t>
+都市空間デザイン
+観光データ分析
+マーケティング分析
+クラスタリング
+需要予測
+行政データ分析
+社会ネットワーク分析
+観光情報学</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>観光地における駅舎建築に関する研究
-nan</t>
+          <t>観光地における駅舎建築に関する研究</t>
         </is>
       </c>
     </row>
@@ -3361,26 +3229,21 @@
           <t>交通工学 ; 輸送最適化</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; オペレーションズリサーチ ; 交通・モビリティ</t>
+          <t>交通工学 ; 輸送最適化 ; 都市・地域政策 ; オペレーションズリサーチ ; 交通・モビリティ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 物流最適化 ; 社会ネットワーク分析</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>交通工学
 輸送最適化
-nan
 都市・地域政策
 オペレーションズリサーチ
 交通・モビリティ
@@ -3393,13 +3256,14 @@
 計画・スケジューリング
 モビリティ設計
 交通需要分析
-ネットワーク設計</t>
+ネットワーク設計
+物流最適化
+社会ネットワーク分析</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>地域公共交通サービス変化時の活動機会変化の計測に関する研究
-nan</t>
+          <t>地域公共交通サービス変化時の活動機会変化の計測に関する研究</t>
         </is>
       </c>
     </row>
@@ -3424,28 +3288,32 @@
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>行動科学 ; 行動経済学 ; 災害・防災研究</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>災害社会学 ; 防災政策 ; リスク評価 ; 行動科学 ; 計算社会科学 ; 学習分析</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
-nan</t>
+災害・防災研究
+災害社会学
+防災政策
+リスク評価
+計算社会科学
+学習分析</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>大学敷地内における大学生の犯罪被害の実態と報告行動の解明
-nan</t>
+          <t>大学敷地内における大学生の犯罪被害の実態と報告行動の解明</t>
         </is>
       </c>
     </row>
@@ -3470,36 +3338,33 @@
           <t>データサイエンス ; 統計モデリング</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>nan ; 機械学習</t>
+          <t>データサイエンス ; 統計モデリング ; 機械学習</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 行政データ分析 ; センサデータ解析 ; 統計学</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>データサイエンス
 統計モデリング
-nan
 機械学習
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+行政データ分析
+センサデータ解析
+統計学</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>職住近接と生活域の拡がりとの関連：GPSデータを用いた検討
-nan</t>
+          <t>職住近接と生活域の拡がりとの関連：GPSデータを用いた検討</t>
         </is>
       </c>
     </row>
@@ -3524,26 +3389,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>nan ; 家族・人口政策 ; 都市・地域政策</t>
+          <t>データ分析 ; 社会システム分析 ; 家族・人口政策 ; 都市・地域政策</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 政策評価</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 家族・人口政策
 都市・地域政策
 家族の経済学
@@ -3553,13 +3413,15 @@
 都市経済
 地域政策
 土地利用
-公共政策評価</t>
+公共政策評価
+行政データ分析
+社会ネットワーク分析
+政策評価</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>人口再配分による食料需給バランス改善への試案 ー「地域で食料が自給できる国土」への視座－
-nan</t>
+          <t>人口再配分による食料需給バランス改善への試案 ー「地域で食料が自給できる国土」への視座－</t>
         </is>
       </c>
     </row>
@@ -3584,37 +3446,34 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 分散システム</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 都市経済
 地域政策
 土地利用
-公共政策評価</t>
+公共政策評価
+行政データ分析
+社会ネットワーク分析
+分散システム</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>都市サービスの長期的な入れ替わりの実態 －2002年と2022年の２時点比較－
-nan</t>
+          <t>都市サービスの長期的な入れ替わりの実態 －2002年と2022年の２時点比較－</t>
         </is>
       </c>
     </row>
@@ -3639,28 +3498,28 @@
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>行動科学 ; 行動経済学</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>行動科学 ; 教育評価 ; 学習分析</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
-nan</t>
+教育評価
+学習分析</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>子どもの体験格差の全国横断的把握 ―学校外での生活行動に着目して－
-nan</t>
+          <t>子どもの体験格差の全国横断的把握 ―学校外での生活行動に着目して－</t>
         </is>
       </c>
     </row>
@@ -3685,28 +3544,34 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>データ分析 ; 社会システム分析 ; 交通・モビリティ</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 社会ネットワーク分析 ; 行政データ分析 ; 推薦システム</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan</t>
+交通・モビリティ
+交通工学
+モビリティ設計
+交通需要分析
+ネットワーク設計
+社会ネットワーク分析
+行政データ分析
+推薦システム</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>シェアサイクル運営者の機会損失改善に向けた自転車再配置における調整台数の検討-茨城県つくば市を事例として-
-nan</t>
+          <t>シェアサイクル運営者の機会損失改善に向けた自転車再配置における調整台数の検討-茨城県つくば市を事例として-</t>
         </is>
       </c>
     </row>
@@ -3731,28 +3596,29 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
+          <t>データ分析 ; 社会システム分析</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan</t>
+社会ネットワーク分析
+行政データ分析
+学習分析</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>アルジェリアにおけるフェルナン・プイヨンのツーリスト・コンプレックスに関する研究
-nan</t>
+          <t>アルジェリアにおけるフェルナン・プイヨンのツーリスト・コンプレックスに関する研究</t>
         </is>
       </c>
     </row>
@@ -3777,28 +3643,39 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
+          <t>データ分析 ; 社会システム分析 ; 交通・モビリティ ; 環境・エネルギー</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 需要予測 ; 社会ネットワーク分析 ; 行政データ分析</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan</t>
+交通・モビリティ
+環境・エネルギー
+交通工学
+モビリティ設計
+交通需要分析
+ネットワーク設計
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+需要予測
+社会ネットワーク分析
+行政データ分析</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>商用FCVの普及に向けた水素ステーション配置とCO2排出量の予測
-nan</t>
+          <t>商用FCVの普及に向けた水素ステーション配置とCO2排出量の予測</t>
         </is>
       </c>
     </row>
@@ -3823,40 +3700,39 @@
           <t>交通工学 ; 輸送最適化</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ ; 交通・モビリティ</t>
+          <t>交通工学 ; 輸送最適化 ; オペレーションズリサーチ ; 交通・モビリティ ; 観光・マーケティング</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>交通工学
 輸送最適化
-nan
 オペレーションズリサーチ
 交通・モビリティ
+観光・マーケティング
 数理最適化
 組合せ最適化
 計画・スケジューリング
 モビリティ設計
 交通需要分析
-ネットワーク設計</t>
+ネットワーク設計
+観光データ分析
+マーケティング分析
+クラスタリング
+需要予測</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>基幹交通の組み合わせ利用を考慮した将来交通需要予測に関する研究
-nan</t>
+          <t>基幹交通の組み合わせ利用を考慮した将来交通需要予測に関する研究</t>
         </is>
       </c>
     </row>
@@ -3881,26 +3757,21 @@
           <t>データサイエンス ; 統計モデリング</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>nan ; GIS・空間分析 ; 建築・空間設計 ; 機械学習</t>
+          <t>データサイエンス ; 統計モデリング ; GIS・空間分析 ; 建築・空間設計 ; 機械学習</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 時系列解析 ; センサデータ解析 ; 統計学</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>データサイエンス
 統計モデリング
-nan
 GIS・空間分析
 建築・空間設計
 機械学習
@@ -3914,13 +3785,15 @@
 都市空間デザイン
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+時系列解析
+センサデータ解析
+統計学</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ETC2.0プローブデータを活用した旅行時間信頼性の時空間的評価
-nan</t>
+          <t>ETC2.0プローブデータを活用した旅行時間信頼性の時空間的評価</t>
         </is>
       </c>
     </row>
@@ -3945,386 +3818,400 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 環境・エネルギー</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
+都市・地域政策
+環境・エネルギー
+都市経済
+地域政策
+土地利用
+公共政策評価
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+行政データ分析
+社会ネットワーク分析
+災害分析</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>自治体におけるグリーンインフラの計画的展開を阻害する要因についての研究</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>張 宇星</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>清代における祭祀行宮の構成と変容—龍王廟を中心に—</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>データ分析 ; 社会システム分析</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>データ分析 ; 社会システム分析</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>データ分析
+社会システム分析
+行政データ分析
+社会ネットワーク分析
+災害分析</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>清代における祭祀行宮の構成と変容—龍王廟を中心に—</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>森下 陽平</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>騒音問題と自己観の関係性：日本・カナダ比較研究</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>データ分析 ; 社会システム分析</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>データ分析 ; 社会システム分析 ; 災害・防災研究</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>災害社会学 ; 防災政策 ; リスク評価 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>データ分析
+社会システム分析
+災害・防災研究
+災害社会学
+防災政策
+リスク評価
+社会ネットワーク分析
+行政データ分析
+災害分析</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>騒音問題と自己観の関係性：日本・カナダ比較研究</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>平林 優希</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>環境配慮意識・行動の自他評価の特性と行動意図の関係</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>行動科学 ; 行動経済学</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>行動科学 ; 行動経済学 ; 環境・エネルギー</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行動科学 ; 政策評価 ; 環境工学</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>行動科学
+行動経済学
+環境・エネルギー
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+政策評価
+環境工学</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>環境配慮意識・行動の自他評価の特性と行動意図の関係</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>中澤 光希</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>都市再生特別地区において多様化する域外貢献の実態と課題に関する研究</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>データ分析 ; 社会システム分析</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 政策評価</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>データ分析
+社会システム分析
 都市・地域政策
 都市経済
 地域政策
 土地利用
-公共政策評価</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>自治体におけるグリーンインフラの計画的展開を阻害する要因についての研究
-nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>張 宇星</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>清代における祭祀行宮の構成と変容—龍王廟を中心に—</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+公共政策評価
+行政データ分析
+社会ネットワーク分析
+政策評価</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>都市再生特別地区において多様化する域外貢献の実態と課題に関する研究</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>草田 弦喜</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>銀座ルールと比較した『日本橋らしさ』に関する研究-東京都日本橋地区を対象として-</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 計算社会科学</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>清代における祭祀行宮の構成と変容—龍王廟を中心に—
-nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>森下 陽平</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>騒音問題と自己観の関係性：日本・カナダ比較研究</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>データ分析 ; 社会システム分析</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>データ分析
-社会システム分析
-nan</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>騒音問題と自己観の関係性：日本・カナダ比較研究
-nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>平林 優希</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>環境配慮意識・行動の自他評価の特性と行動意図の関係</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>行動科学 ; 行動経済学</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>行動科学
-行動経済学
-nan</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>環境配慮意識・行動の自他評価の特性と行動意図の関係
-nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>中澤 光希</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>都市再生特別地区において多様化する域外貢献の実態と課題に関する研究</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>データ分析 ; 社会システム分析</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>nan ; 都市・地域政策</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>データ分析
-社会システム分析
-nan
 都市・地域政策
 都市経済
 地域政策
 土地利用
-公共政策評価</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>都市再生特別地区において多様化する域外貢献の実態と課題に関する研究
-nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>草田 弦喜</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
+公共政策評価
+行政データ分析
+社会ネットワーク分析
+計算社会科学</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
         <is>
           <t>銀座ルールと比較した『日本橋らしさ』に関する研究-東京都日本橋地区を対象として-</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>加藤 優弥</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>スタジアム・アリーナの多機能化に伴う公民連携によるエリアマネジメントに関する研究</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>nan ; 都市・地域政策</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>データ分析 ; 社会システム分析 ; 建築・空間設計 ; スポーツデータ分析</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 行政データ分析 ; 社会ネットワーク分析 ; マーケティング分析</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
-都市・地域政策
-都市経済
-地域政策
-土地利用
-公共政策評価</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>銀座ルールと比較した『日本橋らしさ』に関する研究-東京都日本橋地区を対象として-
-nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>加藤 優弥</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
+建築・空間設計
+スポーツデータ分析
+建築計画
+空間レイアウト生成
+居住空間設計
+都市空間デザイン
+スポーツアナリティクス
+戦術分析
+パフォーマンス分析
+行政データ分析
+社会ネットワーク分析
+マーケティング分析</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
         <is>
           <t>スタジアム・アリーナの多機能化に伴う公民連携によるエリアマネジメントに関する研究</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>水野 瑛介</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>メジャーリーグにおける統計的差別と選好的差別</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>データ分析 ; 社会システム分析 ; 意思決定分析</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 行政データ分析 ; 社会ネットワーク分析 ; 学習分析</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>スタジアム・アリーナの多機能化に伴う公民連携によるエリアマネジメントに関する研究
-nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>水野 瑛介</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>メジャーリーグにおける統計的差別と選好的差別</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>データ分析 ; 社会システム分析</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>nan ; 意思決定分析</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>データ分析
-社会システム分析
-nan
 意思決定分析
 行動意思決定
 実験・行動分析
 ナッジ
-意思決定支援</t>
+意思決定支援
+行政データ分析
+社会ネットワーク分析
+学習分析</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>メジャーリーグにおける統計的差別と選好的差別
-nan</t>
+          <t>メジャーリーグにおける統計的差別と選好的差別</t>
         </is>
       </c>
     </row>
@@ -4349,37 +4236,33 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>nan ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 政策評価・計量分析
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+行政データ分析
+社会ネットワーク分析</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>非罰則規制の犯罪波及効果：渋谷区の路上飲酒禁止条例を事例として
-nan</t>
+          <t>非罰則規制の犯罪波及効果：渋谷区の路上飲酒禁止条例を事例として</t>
         </is>
       </c>
     </row>
@@ -4404,37 +4287,34 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>nan ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; マーケティング分析</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 政策評価・計量分析
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+行政データ分析
+社会ネットワーク分析
+マーケティング分析</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>アメニティに着目した価値あるオフィスビルの要因分析と効果検証
-nan</t>
+          <t>アメニティに着目した価値あるオフィスビルの要因分析と効果検証</t>
         </is>
       </c>
     </row>
@@ -4459,37 +4339,38 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>nan ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 政策評価・計量分析 ; 環境・エネルギー</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行政データ分析 ; 社会ネットワーク分析</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 政策評価・計量分析
+環境・エネルギー
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+行政データ分析
+社会ネットワーク分析</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>グリーンビルディング認証がJ-REITのパフォーマンスに与える影響の実証分析
-nan</t>
+          <t>グリーンビルディング認証がJ-REITのパフォーマンスに与える影響の実証分析</t>
         </is>
       </c>
     </row>
@@ -4514,37 +4395,39 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>nan ; GIS・空間分析</t>
+          <t>データ分析 ; 社会システム分析 ; GIS・空間分析 ; 画像・視覚情報処理</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析</t>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 行政データ分析 ; 社会ネットワーク分析 ; センサデータ解析</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 GIS・空間分析
+画像・視覚情報処理
 GIS
 空間計量
 地理情報分析
-立地分析</t>
+立地分析
+コンピュータビジョン
+画像認識
+行動認識
+マルチモーダル解析
+行政データ分析
+社会ネットワーク分析
+センサデータ解析</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3次元地図更新のための衛星リモートセンシングによる地形計測手法の開発
-nan</t>
+          <t>3次元地図更新のための衛星リモートセンシングによる地形計測手法の開発</t>
         </is>
       </c>
     </row>
@@ -4569,19 +4452,15 @@
           <t>交通工学 ; 輸送最適化 ; 行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ ; 交通・モビリティ</t>
+          <t>交通工学 ; 輸送最適化 ; 行動科学 ; 行動経済学 ; オペレーションズリサーチ ; 交通・モビリティ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 物流最適化 ; 学習分析</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4590,7 +4469,6 @@
 輸送最適化
 行動科学
 行動経済学
-nan
 オペレーションズリサーチ
 交通・モビリティ
 数理最適化
@@ -4598,13 +4476,14 @@
 計画・スケジューリング
 モビリティ設計
 交通需要分析
-ネットワーク設計</t>
+ネットワーク設計
+物流最適化
+学習分析</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>往復移動と滞在行動を考慮したバス頻度問題
-nan</t>
+          <t>往復移動と滞在行動を考慮したバス頻度問題</t>
         </is>
       </c>
     </row>
@@ -4629,26 +4508,21 @@
           <t>経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>nan ; 意思決定分析 ; 建築・空間設計 ; 機械学習</t>
+          <t>経済モデリング ; 意思決定分析 ; 建築・空間設計 ; 機械学習</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 学習分析 ; マーケティング分析</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>経済モデリング
 意思決定分析
-nan
 建築・空間設計
 機械学習
 行動意思決定
@@ -4661,13 +4535,14 @@
 都市空間デザイン
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+学習分析
+マーケティング分析</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>共同住宅におけるEV充電器設置の意思決定メカニズムの解析
-nan</t>
+          <t>共同住宅におけるEV充電器設置の意思決定メカニズムの解析</t>
         </is>
       </c>
     </row>
@@ -4692,19 +4567,15 @@
           <t>交通工学 ; 輸送最適化 ; マルチエージェントシミュレーション ; データサイエンス ; 統計モデリング</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ ; 交通・モビリティ ; 機械学習</t>
+          <t>交通工学 ; 輸送最適化 ; マルチエージェントシミュレーション ; データサイエンス ; 統計モデリング ; オペレーションズリサーチ ; 交通・モビリティ ; 機械学習</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 学習分析</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4714,7 +4585,6 @@
 マルチエージェントシミュレーション
 データサイエンス
 統計モデリング
-nan
 オペレーションズリサーチ
 交通・モビリティ
 機械学習
@@ -4726,13 +4596,13 @@
 ネットワーク設計
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+学習分析</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ミクロ交通シミュレーション利用における機械学習モデルの有効性検討
-nan</t>
+          <t>ミクロ交通シミュレーション利用における機械学習モデルの有効性検討</t>
         </is>
       </c>
     </row>
@@ -4757,26 +4627,21 @@
           <t>交通工学 ; 輸送最適化</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ ; 交通・モビリティ</t>
+          <t>交通工学 ; 輸送最適化 ; オペレーションズリサーチ ; 交通・モビリティ</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 物流最適化 ; 最適化</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>交通工学
 輸送最適化
-nan
 オペレーションズリサーチ
 交通・モビリティ
 数理最適化
@@ -4784,13 +4649,14 @@
 計画・スケジューリング
 モビリティ設計
 交通需要分析
-ネットワーク設計</t>
+ネットワーク設計
+物流最適化
+最適化</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>マクロ交通流理論に基づくグリッドロック現象の分析：タイ・バンコクを対象として
-nan</t>
+          <t>マクロ交通流理論に基づくグリッドロック現象の分析：タイ・バンコクを対象として</t>
         </is>
       </c>
     </row>
@@ -4815,19 +4681,15 @@
           <t>ネットワーク科学 ; グラフ理論 ; 交通工学 ; 輸送最適化 ; データサイエンス ; 統計モデリング</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ ; 交通・モビリティ ; 機械学習 ; ネットワーク・グラフ理論</t>
+          <t>ネットワーク科学 ; グラフ理論 ; 交通工学 ; 輸送最適化 ; データサイエンス ; 統計モデリング ; オペレーションズリサーチ ; 交通・モビリティ ; 機械学習 ; ネットワーク・グラフ理論</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 物流最適化 ; ネットワーク科学</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4838,7 +4700,6 @@
 輸送最適化
 データサイエンス
 統計モデリング
-nan
 オペレーションズリサーチ
 交通・モビリティ
 機械学習
@@ -4854,13 +4715,13 @@
 表現学習
 離散数学
 ネットワーク最適化
-組合せ構造</t>
+組合せ構造
+物流最適化</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>データ同化手法を用いたネットワーク交通流モデルの精度改善及びパラメータ推定
-nan</t>
+          <t>データ同化手法を用いたネットワーク交通流モデルの精度改善及びパラメータ推定</t>
         </is>
       </c>
     </row>
@@ -4885,26 +4746,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>nan ; 都市・地域政策 ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 都市・地域政策
 政策評価・計量分析
 都市経済
@@ -4914,13 +4770,15 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+社会ネットワーク分析
+行政データ分析
+災害分析</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>高速鉄道の開通が都市経済に与える影響の分析
-nan</t>
+          <t>高速鉄道の開通が都市経済に与える影響の分析</t>
         </is>
       </c>
     </row>
@@ -4945,26 +4803,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>nan ; 家族・人口政策 ; 画像・視覚情報処理</t>
+          <t>データ分析 ; 社会システム分析 ; 家族・人口政策 ; 画像・視覚情報処理</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 社会ネットワーク分析 ; 行政データ分析 ; 計算社会科学</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 家族・人口政策
 画像・視覚情報処理
 家族の経済学
@@ -4974,13 +4827,15 @@
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析</t>
+マルチモーダル解析
+社会ネットワーク分析
+行政データ分析
+計算社会科学</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>「認識人口」概念の提案とその実態―市町村に対するポジティブ／ネガティブイメージの分析から－
-nan</t>
+          <t>「認識人口」概念の提案とその実態―市町村に対するポジティブ／ネガティブイメージの分析から－</t>
         </is>
       </c>
     </row>
@@ -5005,26 +4860,21 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>nan ; スポーツデータ分析 ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; スポーツデータ分析 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 行政データ分析 ; マーケティング分析</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 スポーツデータ分析
 政策評価・計量分析
 スポーツアナリティクス
@@ -5033,13 +4883,15 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+社会ネットワーク分析
+行政データ分析
+マーケティング分析</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>プロサッカーチームのリーグ昇降格が街並みに与える影響
-nan</t>
+          <t>プロサッカーチームのリーグ昇降格が街並みに与える影響</t>
         </is>
       </c>
     </row>
@@ -5064,28 +4916,34 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+          <t>データ分析 ; 社会システム分析 ; 観光・マーケティング</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan</t>
+観光・マーケティング
+観光データ分析
+マーケティング分析
+クラスタリング
+需要予測
+社会ネットワーク分析
+行政データ分析
+災害分析</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>コロナ禍以降のバイク需要の持続的拡大の要因：経験財理論に基づく考察
-nan</t>
+          <t>コロナ禍以降のバイク需要の持続的拡大の要因：経験財理論に基づく考察</t>
         </is>
       </c>
     </row>
@@ -5110,37 +4968,34 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>nan ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 学習分析 ; 行政データ分析</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 政策評価・計量分析
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+社会ネットワーク分析
+学習分析
+行政データ分析</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>M-1グランプリのシグナリング効果：動画再生数への影響
-nan</t>
+          <t>M-1グランプリのシグナリング効果：動画再生数への影響</t>
         </is>
       </c>
     </row>
@@ -5165,37 +5020,34 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>nan ; 政策評価・計量分析</t>
+          <t>データ分析 ; 社会システム分析 ; 政策評価・計量分析</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; マーケティング分析</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 政策評価・計量分析
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+行政データ分析
+社会ネットワーク分析
+マーケティング分析</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>花粉が経済活動に与える影響
-nan</t>
+          <t>花粉が経済活動に与える影響</t>
         </is>
       </c>
     </row>
@@ -5220,37 +5072,34 @@
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>nan ; 画像・視覚情報処理</t>
+          <t>データ分析 ; 社会システム分析 ; 画像・視覚情報処理</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
+          <t>コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
-nan
 画像・視覚情報処理
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析</t>
+マルチモーダル解析
+社会ネットワーク分析
+行政データ分析
+災害分析</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>分布北限域における南方系海洋生物の北上とその認識
-nan</t>
+          <t>分布北限域における南方系海洋生物の北上とその認識</t>
         </is>
       </c>
     </row>
@@ -5343,12 +5192,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>会計データ分析 ; 異常検知 ; NLP ; 機械学習</t>
+          <t>会計データ分析 ; 異常検知 ; NLP ; 機械学習 ; 会計・ファイナンス ; テキスト分析・NLP</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 異常検知 ; 行政データ分析 ; センサデータ解析</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5358,9 +5207,20 @@
 異常検知
 NLP
 機械学習
+会計・ファイナンス
+テキスト分析・NLP
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+財務会計
+管理会計
+会計情報システム
+テキストマイニング
+自然言語処理
+感情分析
+社会データ分析
+行政データ分析
+センサデータ解析</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -5403,7 +5263,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 最適化</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5412,7 +5272,8 @@
 スケジューリング
 オペレーションズリサーチ
 組合せ最適化
-計画・スケジューリング</t>
+計画・スケジューリング
+最適化</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -5443,35 +5304,32 @@
           <t>スケジューリング</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ</t>
+          <t>スケジューリング ; オペレーションズリサーチ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 需要予測 ; 学習分析 ; 大規模言語モデル</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>スケジューリング
-nan
 オペレーションズリサーチ
 数理最適化
 組合せ最適化
-計画・スケジューリング</t>
+計画・スケジューリング
+需要予測
+学習分析
+大規模言語モデル</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>中規模学会における発表スケジュール作成モデル
-nan</t>
+          <t>中規模学会における発表スケジュール作成モデル</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5366,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 最適化</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5517,7 +5375,8 @@
 数理最適化
 オペレーションズリサーチ
 組合せ最適化
-計画・スケジューリング</t>
+計画・スケジューリング
+最適化</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -5555,12 +5414,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>医療データ分析 ; 統計解析 ; 都市・地域政策 ; 政策評価・計量分析</t>
+          <t>医療データ分析 ; 統計解析 ; 都市・地域政策 ; 政策評価・計量分析 ; 医療・ヘルスデータ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5570,6 +5429,7 @@
 統計解析
 都市・地域政策
 政策評価・計量分析
+医療・ヘルスデータ
 都市経済
 地域政策
 土地利用
@@ -5577,7 +5437,12 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+生体情報解析
+ヘルスデータサイエンス
+社会ネットワーク分析
+行政データ分析
+学習分析</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5615,12 +5480,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>テキスト分析 ; 感情分析 ; ネットワーク・グラフ理論</t>
+          <t>テキスト分析 ; 感情分析 ; ネットワーク・グラフ理論 ; テキスト分析・NLP</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
+          <t>グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 社会ネットワーク分析 ; 学習分析</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5629,10 +5494,15 @@
 テキスト分析
 感情分析
 ネットワーク・グラフ理論
+テキスト分析・NLP
 グラフ理論
 離散数学
 ネットワーク最適化
-組合せ構造</t>
+組合せ構造
+自然言語処理
+社会データ分析
+社会ネットワーク分析
+学習分析</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -5675,7 +5545,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 最適化</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5687,7 +5557,8 @@
 計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+最適化</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5725,15 +5596,31 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>統計解析 ; 医療データ</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>統計解析 ; 医療データ ; 医療・ヘルスデータ ; 環境・エネルギー</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行政データ分析 ; 学習分析 ; センサデータ解析</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>データ解析
 統計解析
-医療データ</t>
+医療データ
+医療・ヘルスデータ
+環境・エネルギー
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+環境政策
+エネルギーシステム
+脱炭素分析
+持続可能性評価
+行政データ分析
+学習分析
+センサデータ解析</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -5771,12 +5658,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>スケジューリング ; 数理最適化 ; 労働経済・就職マッチング ; オペレーションズリサーチ</t>
+          <t>スケジューリング ; 数理最適化 ; 労働経済・就職マッチング ; オペレーションズリサーチ ; 観光・マーケティング</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 最適化</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5785,12 +5672,18 @@
 数理最適化
 労働経済・就職マッチング
 オペレーションズリサーチ
+観光・マーケティング
 労働経済
 人的資本
 就職マッチング
 採用市場設計
 組合せ最適化
-計画・スケジューリング</t>
+計画・スケジューリング
+観光データ分析
+マーケティング分析
+クラスタリング
+需要予測
+最適化</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -5828,15 +5721,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ビッグデータ解析 ; 生体情報</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>ビッグデータ解析 ; 生体情報 ; 医療・ヘルスデータ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 行政データ分析 ; センサデータ解析 ; 学習分析</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>データ解析
 ビッグデータ解析
-生体情報</t>
+生体情報
+医療・ヘルスデータ
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+行政データ分析
+センサデータ解析
+学習分析</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5879,7 +5784,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 待ち行列理論 ; サービス工学 ; システム性能評価</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 待ち行列理論 ; サービス工学 ; システム性能評価 ; 学習分析 ; 需要予測</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5891,7 +5796,9 @@
 予測モデリング
 表現学習
 サービス工学
-システム性能評価</t>
+システム性能評価
+学習分析
+需要予測</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5929,15 +5836,30 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>テキスト分析 ; 社会データ</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>テキスト分析 ; 社会データ ; テキスト分析・NLP ; 医療・ヘルスデータ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; 行政データ分析</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>テキストマイニング
 テキスト分析
-社会データ</t>
+社会データ
+テキスト分析・NLP
+医療・ヘルスデータ
+自然言語処理
+感情分析
+社会データ分析
+医療データ分析
+生体情報解析
+ヘルスデータサイエンス
+統計解析
+社会ネットワーク分析
+行政データ分析</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -5975,12 +5897,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>自然言語処理 ; 金融データ ; 保険・金融行動</t>
+          <t>自然言語処理 ; 金融データ ; 保険・金融行動 ; テキスト分析・NLP</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 大規模言語モデル ; 学習分析</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5989,10 +5911,16 @@
 自然言語処理
 金融データ
 保険・金融行動
+テキスト分析・NLP
 行動ファイナンス
 金融市場分析
 ESG投資
-企業財務</t>
+企業財務
+テキストマイニング
+感情分析
+社会データ分析
+大規模言語モデル
+学習分析</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6030,15 +5958,26 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>会計データ分析 ; 時系列</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>会計データ分析 ; 時系列 ; 会計・ファイナンス</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 行政データ分析 ; センサデータ解析 ; 学習分析</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>会計
 会計データ分析
-時系列</t>
+時系列
+会計・ファイナンス
+財務会計
+管理会計
+会計情報システム
+行政データ分析
+センサデータ解析
+学習分析</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6081,7 +6020,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 最適化</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -6094,7 +6033,8 @@
 計画・スケジューリング
 グラフ理論
 離散数学
-組合せ構造</t>
+組合せ構造
+最適化</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6137,7 +6077,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 推薦システム ; 学習分析 ; 組合せ最適化</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6147,7 +6087,9 @@
 推薦システム
 統計的学習
 予測モデリング
-表現学習</t>
+表現学習
+学習分析
+組合せ最適化</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -6185,14 +6127,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>クラスタリング ; 観光データ</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>クラスタリング ; 観光データ ; 観光・マーケティング</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 観光情報学 ; 学習分析</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>クラスタリング
-観光データ</t>
+観光データ
+観光・マーケティング
+観光データ分析
+マーケティング分析
+需要予測
+観光情報学
+学習分析</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -6235,7 +6187,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 物流最適化</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6244,7 +6196,8 @@
 スケジューリング
 オペレーションズリサーチ
 組合せ最適化
-計画・スケジューリング</t>
+計画・スケジューリング
+物流最適化</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6282,12 +6235,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>確率モデル ; テキスト解析 ; 意思決定分析 ; 政策評価・計量分析</t>
+          <t>確率モデル ; テキスト解析 ; 意思決定分析 ; 政策評価・計量分析 ; テキスト分析・NLP</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 学習分析 ; センサデータ解析 ; 行政データ分析</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6297,6 +6250,7 @@
 テキスト解析
 意思決定分析
 政策評価・計量分析
+テキスト分析・NLP
 行動意思決定
 実験・行動分析
 ナッジ
@@ -6304,7 +6258,14 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析</t>
+実証分析
+テキストマイニング
+自然言語処理
+感情分析
+社会データ分析
+学習分析
+センサデータ解析
+行政データ分析</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -6335,25 +6296,20 @@
           <t>シミュレーション</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>nan ; オペレーションズリサーチ ; 災害・防災研究</t>
+          <t>シミュレーション ; オペレーションズリサーチ ; 災害・防災研究</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 災害社会学 ; 防災政策 ; リスク評価</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 災害社会学 ; 防災政策 ; リスク評価 ; 物流最適化 ; 最適化</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>シミュレーション
-nan
 オペレーションズリサーチ
 災害・防災研究
 数理最適化
@@ -6361,13 +6317,14 @@
 計画・スケジューリング
 災害社会学
 防災政策
-リスク評価</t>
+リスク評価
+物流最適化
+最適化</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>実データを用いた平常時の収益性と災害時の孤立リスクを考慮したドローン配送基地の施設立地最適化
-nan</t>
+          <t>実データを用いた平常時の収益性と災害時の孤立リスクを考慮したドローン配送基地の施設立地最適化</t>
         </is>
       </c>
     </row>
@@ -6399,12 +6356,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>金融データ分析 ; 会計 ; 保険・金融行動 ; 都市・地域政策</t>
+          <t>金融データ分析 ; 会計 ; 保険・金融行動 ; 都市・地域政策 ; 会計・ファイナンス</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 行政データ分析 ; 品質管理 ; 学習分析</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6413,6 +6370,7 @@
 金融データ分析
 保険・金融行動
 都市・地域政策
+会計・ファイナンス
 行動ファイナンス
 金融市場分析
 ESG投資
@@ -6420,7 +6378,14 @@
 都市経済
 地域政策
 土地利用
-公共政策評価</t>
+公共政策評価
+会計データ分析
+財務会計
+管理会計
+会計情報システム
+行政データ分析
+品質管理
+学習分析</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">

--- a/generated/students_enriched.xlsx
+++ b/generated/students_enriched.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; マーケティング分析 ; 学習分析</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -524,9 +524,7 @@
 意思決定支援
 統計的学習
 予測モデリング
-表現学習
-マーケティング分析
-学習分析</t>
+表現学習</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -564,7 +562,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; マーケティング分析</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -588,8 +586,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-マーケティング分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -627,7 +624,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 学習分析 ; マーケティング分析</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -646,9 +643,7 @@
 意思決定支援
 統計的学習
 予測モデリング
-表現学習
-学習分析
-マーケティング分析</t>
+表現学習</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -686,7 +681,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; マーケティング分析</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -709,8 +704,7 @@
 計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習
-マーケティング分析</t>
+表現学習</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -748,7 +742,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 行動科学 ; 学習分析 ; マーケティング分析</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -764,9 +758,7 @@
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析
-学習分析
-マーケティング分析</t>
+マルチモーダル解析</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -804,7 +796,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行動科学 ; 経営工学</t>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -820,8 +812,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-経営工学</t>
+実証分析</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -859,7 +850,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 社会ネットワーク分析 ; 行政データ分析 ; 計算社会科学</t>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,10 +861,7 @@
 安定マッチング
 資源配分
 メカニズムデザイン
-協力ゲーム・非協力ゲーム
-社会ネットワーク分析
-行政データ分析
-計算社会科学</t>
+協力ゲーム・非協力ゲーム</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -911,7 +899,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 最適化</t>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -930,8 +918,7 @@
 計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習
-最適化</t>
+表現学習</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -969,7 +956,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 行政データ分析 ; シミュレーション</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -989,10 +976,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-社会ネットワーク分析
-行政データ分析
-シミュレーション</t>
+実証分析</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1030,7 +1014,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1044,8 +1028,7 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン
-最適化</t>
+都市空間デザイン</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1083,7 +1066,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
+          <t>スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1093,10 +1076,7 @@
 スポーツデータ分析
 スポーツアナリティクス
 戦術分析
-パフォーマンス分析
-社会ネットワーク分析
-行政データ分析
-学習分析</t>
+パフォーマンス分析</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1134,7 +1114,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; ネットワーク科学 ; 知識グラフ ; 数理モデリング</t>
+          <t>グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1144,9 +1124,7 @@
 ネットワーク・グラフ理論
 離散数学
 ネットワーク最適化
-組合せ構造
-知識グラフ
-数理モデリング</t>
+組合せ構造</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; ネットワーク科学</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1247,7 +1225,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1273,8 +1251,7 @@
 表現学習
 環境政策
 脱炭素分析
-持続可能性評価
-最適化</t>
+持続可能性評価</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1312,7 +1289,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 物流最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1320,8 +1297,7 @@
           <t>数理最適化
 組合せ最適化
 オペレーションズリサーチ
-計画・スケジューリング
-物流最適化</t>
+計画・スケジューリング</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1359,7 +1335,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 行動科学 ; 学習分析 ; 最適化</t>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1370,9 +1346,7 @@
 行動意思決定
 実験・行動分析
 ナッジ
-意思決定支援
-学習分析
-最適化</t>
+意思決定支援</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1410,7 +1384,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1426,8 +1400,7 @@
 計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習
-最適化</t>
+表現学習</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1465,7 +1438,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 行政データ分析 ; 社会ネットワーク分析 ; センサデータ解析</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,10 +1458,7 @@
 医療データ分析
 生体情報解析
 ヘルスデータサイエンス
-統計解析
-行政データ分析
-社会ネットワーク分析
-センサデータ解析</t>
+統計解析</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1526,7 +1496,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 学習分析 ; マーケティング分析 ; 組合せ最適化</t>
+          <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1542,10 +1512,7 @@
 交通工学
 モビリティ設計
 交通需要分析
-ネットワーク設計
-学習分析
-マーケティング分析
-組合せ最適化</t>
+ネットワーク設計</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1583,7 +1550,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 分散システム ; 社会ネットワーク分析 ; 行政データ分析</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1593,10 +1560,7 @@
 オペレーションズリサーチ
 数理最適化
 組合せ最適化
-計画・スケジューリング
-分散システム
-社会ネットワーク分析
-行政データ分析</t>
+計画・スケジューリング</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1634,7 +1598,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1655,10 +1619,7 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン
-社会ネットワーク分析
-行政データ分析
-学習分析</t>
+都市空間デザイン</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1696,7 +1657,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 行動科学 ; 学習分析 ; 認知科学</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1711,9 +1672,7 @@
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析
-学習分析
-認知科学</t>
+マルチモーダル解析</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1751,7 +1710,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 計算社会科学</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1767,10 +1726,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-行政データ分析
-社会ネットワーク分析
-計算社会科学</t>
+実証分析</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1808,7 +1764,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 社会ネットワーク分析 ; 行政データ分析 ; センサデータ解析</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1828,10 +1784,7 @@
 テキストマイニング
 自然言語処理
 感情分析
-社会データ分析
-社会ネットワーク分析
-行政データ分析
-センサデータ解析</t>
+社会データ分析</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1869,7 +1822,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; マーケティング分析 ; 学習分析</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1888,9 +1841,7 @@
 意思決定支援
 統計的学習
 予測モデリング
-表現学習
-マーケティング分析
-学習分析</t>
+表現学習</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1928,7 +1879,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 学習分析</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1949,10 +1900,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-行政データ分析
-社会ネットワーク分析
-学習分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1990,7 +1938,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 物流最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1998,8 +1946,7 @@
           <t>数理最適化
 組合せ最適化
 オペレーションズリサーチ
-計画・スケジューリング
-物流最適化</t>
+計画・スケジューリング</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2037,7 +1984,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 社会ネットワーク分析 ; 行政データ分析 ; 異常検知</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2052,10 +1999,7 @@
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析
-社会ネットワーク分析
-行政データ分析
-異常検知</t>
+マルチモーダル解析</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2093,7 +2037,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>待ち行列理論 ; サービス工学 ; システム性能評価 ; 社会ネットワーク分析 ; 行政データ分析 ; 推薦システム</t>
+          <t>待ち行列理論 ; サービス工学 ; システム性能評価</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2103,10 +2047,7 @@
 サービス・待ち行列
 待ち行列理論
 サービス工学
-システム性能評価
-社会ネットワーク分析
-行政データ分析
-推薦システム</t>
+システム性能評価</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2144,7 +2085,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; マーケティング分析</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2165,10 +2106,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-行政データ分析
-社会ネットワーク分析
-マーケティング分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2206,7 +2144,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>災害社会学 ; 防災政策 ; リスク評価 ; 災害分析 ; 行政データ分析 ; 社会ネットワーク分析</t>
+          <t>災害社会学 ; 防災政策 ; リスク評価</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2216,10 +2154,7 @@
 災害・防災研究
 災害社会学
 防災政策
-リスク評価
-災害分析
-行政データ分析
-社会ネットワーク分析</t>
+リスク評価</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2257,7 +2192,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 社会ネットワーク分析 ; 行政データ分析 ; 政策評価</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2273,10 +2208,7 @@
 社会福祉政策
 地域福祉
 子育て支援
-非営利組織論
-社会ネットワーク分析
-行政データ分析
-政策評価</t>
+非営利組織論</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2314,7 +2246,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 社会ネットワーク分析 ; 行政データ分析 ; 計算社会科学</t>
+          <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2325,10 +2257,7 @@
 社会福祉政策
 地域福祉
 子育て支援
-非営利組織論
-社会ネットワーク分析
-行政データ分析
-計算社会科学</t>
+非営利組織論</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2366,7 +2295,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2382,10 +2311,7 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン
-行政データ分析
-社会ネットワーク分析
-災害分析</t>
+都市空間デザイン</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2423,7 +2349,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 農業情報学</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2439,10 +2365,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-行政データ分析
-社会ネットワーク分析
-農業情報学</t>
+実証分析</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2480,7 +2403,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 学習分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2496,10 +2419,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-行政データ分析
-社会ネットワーク分析
-学習分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2537,7 +2457,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 推薦システム</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2548,10 +2468,7 @@
 都市経済
 地域政策
 土地利用
-公共政策評価
-行政データ分析
-社会ネットワーク分析
-推薦システム</t>
+公共政策評価</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2589,7 +2506,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2610,10 +2527,7 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン
-行政データ分析
-社会ネットワーク分析
-災害分析</t>
+都市空間デザイン</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2651,7 +2565,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2677,10 +2591,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-行政データ分析
-社会ネットワーク分析
-災害分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2718,7 +2629,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 災害分析 ; 行政データ分析 ; 社会ネットワーク分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2743,10 +2654,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-災害分析
-行政データ分析
-社会ネットワーク分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2784,7 +2692,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>災害社会学 ; 防災政策 ; リスク評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
+          <t>災害社会学 ; 防災政策 ; リスク評価</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2794,10 +2702,7 @@
 災害・防災研究
 災害社会学
 防災政策
-リスク評価
-行政データ分析
-社会ネットワーク分析
-災害分析</t>
+リスク評価</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2835,7 +2740,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2851,10 +2756,7 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン
-社会ネットワーク分析
-行政データ分析
-学習分析</t>
+都市空間デザイン</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2892,7 +2794,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 社会ネットワーク分析 ; 農業情報学 ; 行政データ分析</t>
+          <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2903,10 +2805,7 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン
-社会ネットワーク分析
-農業情報学
-行政データ分析</t>
+都市空間デザイン</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2944,7 +2843,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 行政データ分析 ; 社会ネットワーク分析 ; 都市計画</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2965,10 +2864,7 @@
 建築計画
 空間レイアウト生成
 居住空間設計
-都市空間デザイン
-行政データ分析
-社会ネットワーク分析
-都市計画</t>
+都市空間デザイン</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3006,7 +2902,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 社会ネットワーク分析 ; ネットワーク科学 ; 行政データ分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3021,9 +2917,7 @@
 公共政策評価
 離散数学
 ネットワーク最適化
-組合せ構造
-社会ネットワーク分析
-行政データ分析</t>
+組合せ構造</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3061,7 +2955,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3077,10 +2971,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-行政データ分析
-社会ネットワーク分析
-災害分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3118,7 +3009,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 行政データ分析 ; 社会ネットワーク分析 ; 観光情報学</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3139,10 +3030,7 @@
 観光データ分析
 マーケティング分析
 クラスタリング
-需要予測
-行政データ分析
-社会ネットワーク分析
-観光情報学</t>
+需要予測</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3180,7 +3068,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 行政データ分析 ; 社会ネットワーク分析 ; 観光情報学</t>
+          <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3196,10 +3084,7 @@
 観光データ分析
 マーケティング分析
 クラスタリング
-需要予測
-行政データ分析
-社会ネットワーク分析
-観光情報学</t>
+需要予測</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3237,7 +3122,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 物流最適化 ; 社会ネットワーク分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3256,9 +3141,7 @@
 計画・スケジューリング
 モビリティ設計
 交通需要分析
-ネットワーク設計
-物流最適化
-社会ネットワーク分析</t>
+ネットワーク設計</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3296,7 +3179,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>災害社会学 ; 防災政策 ; リスク評価 ; 行動科学 ; 計算社会科学 ; 学習分析</t>
+          <t>災害社会学 ; 防災政策 ; リスク評価</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3306,9 +3189,7 @@
 災害・防災研究
 災害社会学
 防災政策
-リスク評価
-計算社会科学
-学習分析</t>
+リスク評価</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3346,7 +3227,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 行政データ分析 ; センサデータ解析 ; 統計学</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3356,10 +3237,7 @@
 機械学習
 統計的学習
 予測モデリング
-表現学習
-行政データ分析
-センサデータ解析
-統計学</t>
+表現学習</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3397,7 +3275,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 政策評価</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3413,10 +3291,7 @@
 都市経済
 地域政策
 土地利用
-公共政策評価
-行政データ分析
-社会ネットワーク分析
-政策評価</t>
+公共政策評価</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3454,7 +3329,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 分散システム</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3465,10 +3340,7 @@
 都市経済
 地域政策
 土地利用
-公共政策評価
-行政データ分析
-社会ネットワーク分析
-分散システム</t>
+公共政策評価</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3506,15 +3378,13 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>行動科学 ; 教育評価 ; 学習分析</t>
+          <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>行動科学
-行動経済学
-教育評価
-学習分析</t>
+行動経済学</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3552,7 +3422,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 社会ネットワーク分析 ; 行政データ分析 ; 推薦システム</t>
+          <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3563,10 +3433,7 @@
 交通工学
 モビリティ設計
 交通需要分析
-ネットワーク設計
-社会ネットワーク分析
-行政データ分析
-推薦システム</t>
+ネットワーク設計</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3604,16 +3471,13 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
+          <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>データ分析
-社会システム分析
-社会ネットワーク分析
-行政データ分析
-学習分析</t>
+社会システム分析</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3651,7 +3515,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 需要予測 ; 社会ネットワーク分析 ; 行政データ分析</t>
+          <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3667,10 +3531,7 @@
 環境政策
 エネルギーシステム
 脱炭素分析
-持続可能性評価
-需要予測
-社会ネットワーク分析
-行政データ分析</t>
+持続可能性評価</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3765,7 +3626,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 時系列解析 ; センサデータ解析 ; 統計学</t>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3785,10 +3646,7 @@
 都市空間デザイン
 統計的学習
 予測モデリング
-表現学習
-時系列解析
-センサデータ解析
-統計学</t>
+表現学習</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3826,7 +3684,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3842,10 +3700,7 @@
 環境政策
 エネルギーシステム
 脱炭素分析
-持続可能性評価
-行政データ分析
-社会ネットワーク分析
-災害分析</t>
+持続可能性評価</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3883,16 +3738,13 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>行政データ分析 ; 社会ネットワーク分析 ; 災害分析</t>
+          <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>データ分析
-社会システム分析
-行政データ分析
-社会ネットワーク分析
-災害分析</t>
+社会システム分析</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3930,7 +3782,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>災害社会学 ; 防災政策 ; リスク評価 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析</t>
+          <t>災害社会学 ; 防災政策 ; リスク評価</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3940,10 +3792,7 @@
 災害・防災研究
 災害社会学
 防災政策
-リスク評価
-社会ネットワーク分析
-行政データ分析
-災害分析</t>
+リスク評価</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3981,7 +3830,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行動科学 ; 政策評価 ; 環境工学</t>
+          <t>環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3992,9 +3841,7 @@
 環境政策
 エネルギーシステム
 脱炭素分析
-持続可能性評価
-政策評価
-環境工学</t>
+持続可能性評価</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4032,7 +3879,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 政策評価</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4043,10 +3890,7 @@
 都市経済
 地域政策
 土地利用
-公共政策評価
-行政データ分析
-社会ネットワーク分析
-政策評価</t>
+公共政策評価</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4084,7 +3928,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 行政データ分析 ; 社会ネットワーク分析 ; 計算社会科学</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4095,10 +3939,7 @@
 都市経済
 地域政策
 土地利用
-公共政策評価
-行政データ分析
-社会ネットワーク分析
-計算社会科学</t>
+公共政策評価</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4136,7 +3977,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 行政データ分析 ; 社会ネットワーク分析 ; マーケティング分析</t>
+          <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4151,10 +3992,7 @@
 都市空間デザイン
 スポーツアナリティクス
 戦術分析
-パフォーマンス分析
-行政データ分析
-社会ネットワーク分析
-マーケティング分析</t>
+パフォーマンス分析</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4192,7 +4030,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 行政データ分析 ; 社会ネットワーク分析 ; 学習分析</t>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4203,10 +4041,7 @@
 行動意思決定
 実験・行動分析
 ナッジ
-意思決定支援
-行政データ分析
-社会ネットワーク分析
-学習分析</t>
+意思決定支援</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4244,7 +4079,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析</t>
+          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4255,9 +4090,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-行政データ分析
-社会ネットワーク分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4295,7 +4128,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; マーケティング分析</t>
+          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4306,10 +4139,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-行政データ分析
-社会ネットワーク分析
-マーケティング分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4347,7 +4177,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行政データ分析 ; 社会ネットワーク分析</t>
+          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4363,9 +4193,7 @@
 環境政策
 エネルギーシステム
 脱炭素分析
-持続可能性評価
-行政データ分析
-社会ネットワーク分析</t>
+持続可能性評価</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4403,7 +4231,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 行政データ分析 ; 社会ネットワーク分析 ; センサデータ解析</t>
+          <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4419,10 +4247,7 @@
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析
-行政データ分析
-社会ネットワーク分析
-センサデータ解析</t>
+マルチモーダル解析</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4460,7 +4285,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 物流最適化 ; 学習分析</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4476,9 +4301,7 @@
 計画・スケジューリング
 モビリティ設計
 交通需要分析
-ネットワーク設計
-物流最適化
-学習分析</t>
+ネットワーク設計</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4516,7 +4339,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 学習分析 ; マーケティング分析</t>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4535,9 +4358,7 @@
 都市空間デザイン
 統計的学習
 予測モデリング
-表現学習
-学習分析
-マーケティング分析</t>
+表現学習</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4575,7 +4396,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 学習分析</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4596,8 +4417,7 @@
 ネットワーク設計
 統計的学習
 予測モデリング
-表現学習
-学習分析</t>
+表現学習</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4635,7 +4455,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 物流最適化 ; 最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4649,9 +4469,7 @@
 計画・スケジューリング
 モビリティ設計
 交通需要分析
-ネットワーク設計
-物流最適化
-最適化</t>
+ネットワーク設計</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4689,7 +4507,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 物流最適化 ; ネットワーク科学</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4715,8 +4533,7 @@
 表現学習
 離散数学
 ネットワーク最適化
-組合せ構造
-物流最適化</t>
+組合せ構造</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4754,7 +4571,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4770,10 +4587,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-社会ネットワーク分析
-行政データ分析
-災害分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4811,7 +4625,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 社会ネットワーク分析 ; 行政データ分析 ; 計算社会科学</t>
+          <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4827,10 +4641,7 @@
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析
-社会ネットワーク分析
-行政データ分析
-計算社会科学</t>
+マルチモーダル解析</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4868,7 +4679,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 行政データ分析 ; マーケティング分析</t>
+          <t>スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4883,10 +4694,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-社会ネットワーク分析
-行政データ分析
-マーケティング分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4924,7 +4732,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析</t>
+          <t>観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4935,10 +4743,7 @@
 観光データ分析
 マーケティング分析
 クラスタリング
-需要予測
-社会ネットワーク分析
-行政データ分析
-災害分析</t>
+需要予測</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4976,7 +4781,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 社会ネットワーク分析 ; 学習分析 ; 行政データ分析</t>
+          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4987,10 +4792,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-社会ネットワーク分析
-学習分析
-行政データ分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5028,7 +4830,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 行政データ分析 ; 社会ネットワーク分析 ; マーケティング分析</t>
+          <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5039,10 +4841,7 @@
 政策評価
 計量経済学
 統計的因果推論
-実証分析
-行政データ分析
-社会ネットワーク分析
-マーケティング分析</t>
+実証分析</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5080,7 +4879,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 社会ネットワーク分析 ; 行政データ分析 ; 災害分析</t>
+          <t>コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5091,10 +4890,7 @@
 コンピュータビジョン
 画像認識
 行動認識
-マルチモーダル解析
-社会ネットワーク分析
-行政データ分析
-災害分析</t>
+マルチモーダル解析</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5197,7 +4993,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 異常検知 ; 行政データ分析 ; センサデータ解析</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5218,9 +5014,7 @@
 テキストマイニング
 自然言語処理
 感情分析
-社会データ分析
-行政データ分析
-センサデータ解析</t>
+社会データ分析</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -5263,7 +5057,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5272,8 +5066,7 @@
 スケジューリング
 オペレーションズリサーチ
 組合せ最適化
-計画・スケジューリング
-最適化</t>
+計画・スケジューリング</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -5312,7 +5105,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 需要予測 ; 学習分析 ; 大規模言語モデル</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5321,10 +5114,7 @@
 オペレーションズリサーチ
 数理最適化
 組合せ最適化
-計画・スケジューリング
-需要予測
-学習分析
-大規模言語モデル</t>
+計画・スケジューリング</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -5366,7 +5156,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5375,8 +5165,7 @@
 数理最適化
 オペレーションズリサーチ
 組合せ最適化
-計画・スケジューリング
-最適化</t>
+計画・スケジューリング</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -5419,7 +5208,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; 行政データ分析 ; 学習分析</t>
+          <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5439,10 +5228,7 @@
 統計的因果推論
 実証分析
 生体情報解析
-ヘルスデータサイエンス
-社会ネットワーク分析
-行政データ分析
-学習分析</t>
+ヘルスデータサイエンス</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5485,7 +5271,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 社会ネットワーク分析 ; 学習分析</t>
+          <t>グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5500,9 +5286,7 @@
 ネットワーク最適化
 組合せ構造
 自然言語処理
-社会データ分析
-社会ネットワーク分析
-学習分析</t>
+社会データ分析</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -5545,7 +5329,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5557,8 +5341,7 @@
 計画・スケジューリング
 統計的学習
 予測モデリング
-表現学習
-最適化</t>
+表現学習</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -5601,7 +5384,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価 ; 行政データ分析 ; 学習分析 ; センサデータ解析</t>
+          <t>医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5617,10 +5400,7 @@
 環境政策
 エネルギーシステム
 脱炭素分析
-持続可能性評価
-行政データ分析
-学習分析
-センサデータ解析</t>
+持続可能性評価</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -5663,7 +5443,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 最適化</t>
+          <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5682,8 +5462,7 @@
 観光データ分析
 マーケティング分析
 クラスタリング
-需要予測
-最適化</t>
+需要予測</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -5726,7 +5505,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 行政データ分析 ; センサデータ解析 ; 学習分析</t>
+          <t>医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5738,10 +5517,7 @@
 医療データ分析
 生体情報解析
 ヘルスデータサイエンス
-統計解析
-行政データ分析
-センサデータ解析
-学習分析</t>
+統計解析</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5784,7 +5560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 待ち行列理論 ; サービス工学 ; システム性能評価 ; 学習分析 ; 需要予測</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 待ち行列理論 ; サービス工学 ; システム性能評価</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5796,9 +5572,7 @@
 予測モデリング
 表現学習
 サービス工学
-システム性能評価
-学習分析
-需要予測</t>
+システム性能評価</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5841,7 +5615,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 社会ネットワーク分析 ; 行政データ分析</t>
+          <t>テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5857,9 +5631,7 @@
 医療データ分析
 生体情報解析
 ヘルスデータサイエンス
-統計解析
-社会ネットワーク分析
-行政データ分析</t>
+統計解析</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -5902,7 +5674,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 大規模言語モデル ; 学習分析</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5918,9 +5690,7 @@
 企業財務
 テキストマイニング
 感情分析
-社会データ分析
-大規模言語モデル
-学習分析</t>
+社会データ分析</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -5963,7 +5733,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 行政データ分析 ; センサデータ解析 ; 学習分析</t>
+          <t>会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5974,10 +5744,7 @@
 会計・ファイナンス
 財務会計
 管理会計
-会計情報システム
-行政データ分析
-センサデータ解析
-学習分析</t>
+会計情報システム</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6020,7 +5787,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; 最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -6033,8 +5800,7 @@
 計画・スケジューリング
 グラフ理論
 離散数学
-組合せ構造
-最適化</t>
+組合せ構造</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6077,7 +5843,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 推薦システム ; 学習分析 ; 組合せ最適化</t>
+          <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6087,9 +5853,7 @@
 推薦システム
 統計的学習
 予測モデリング
-表現学習
-学習分析
-組合せ最適化</t>
+表現学習</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -6132,7 +5896,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測 ; 観光情報学 ; 学習分析</t>
+          <t>観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6142,9 +5906,7 @@
 観光・マーケティング
 観光データ分析
 マーケティング分析
-需要予測
-観光情報学
-学習分析</t>
+需要予測</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -6187,7 +5949,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 物流最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6196,8 +5958,7 @@
 スケジューリング
 オペレーションズリサーチ
 組合せ最適化
-計画・スケジューリング
-物流最適化</t>
+計画・スケジューリング</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6240,7 +6001,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 学習分析 ; センサデータ解析 ; 行政データ分析</t>
+          <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6262,10 +6023,7 @@
 テキストマイニング
 自然言語処理
 感情分析
-社会データ分析
-学習分析
-センサデータ解析
-行政データ分析</t>
+社会データ分析</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -6304,7 +6062,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 災害社会学 ; 防災政策 ; リスク評価 ; 物流最適化 ; 最適化</t>
+          <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 災害社会学 ; 防災政策 ; リスク評価</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6317,9 +6075,7 @@
 計画・スケジューリング
 災害社会学
 防災政策
-リスク評価
-物流最適化
-最適化</t>
+リスク評価</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -6361,7 +6117,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; 行政データ分析 ; 品質管理 ; 学習分析</t>
+          <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6382,10 +6138,7 @@
 会計データ分析
 財務会計
 管理会計
-会計情報システム
-行政データ分析
-品質管理
-学習分析</t>
+会計情報システム</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">

--- a/generated/students_enriched.xlsx
+++ b/generated/students_enriched.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,40 +437,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>student_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>group</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>overview_field</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>research_content</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>research_field</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>detailed_research_field</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>field_text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>content_text</t>
         </is>
@@ -482,33 +487,34 @@
           <t>中島 元毅</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>日本の就活市場における新卒採用に関する研究</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>経済モデリング ; 意思決定分析 ; 労働経済・就職マッチング ; 機械学習</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>経済モデリング
 意思決定分析
@@ -527,7 +533,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>日本の就活市場における新卒採用に関する研究</t>
         </is>
@@ -539,33 +545,34 @@
           <t>荒金 志紀</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>結婚の意思決定に対する独身税の効果と税制度の提案</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>経済モデリング ; 意思決定分析 ; 家族・人口政策 ; 機械学習 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>経済モデリング
 意思決定分析
@@ -589,7 +596,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>結婚の意思決定に対する独身税の効果と税制度の提案</t>
         </is>
@@ -601,33 +608,34 @@
           <t>小峯 拓也</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>学生の選考情報を利用した就活支援サービスに関する研究</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>経済モデリング ; 意思決定分析 ; 労働経済・就職マッチング ; 機械学習</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>経済モデリング
 意思決定分析
@@ -646,7 +654,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>学生の選考情報を利用した就活支援サービスに関する研究</t>
         </is>
@@ -658,33 +666,34 @@
           <t>貫井 虹希</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>最適停止問題を用いた就活市場の分析と改善提案</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; 経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; 経済モデリング ; 意思決定分析 ; 労働経済・就職マッチング ; オペレーションズリサーチ ; 機械学習</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>数理最適化
 組合せ最適化
@@ -707,7 +716,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>最適停止問題を用いた就活市場の分析と改善提案</t>
         </is>
@@ -719,33 +728,34 @@
           <t>安達 未晴</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>視線計測を用いた保険加入行動の分析</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学 ; 保険・金融行動 ; 画像・視覚情報処理</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
@@ -761,7 +771,7 @@
 マルチモーダル解析</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>視線計測を用いた保険加入行動の分析</t>
         </is>
@@ -773,33 +783,34 @@
           <t>YANG LUXI</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>価値観が失敗の対処行動に与える影響-失敗体験の重大性と領域を考えて-</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学 ; 意思決定分析 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
@@ -815,7 +826,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>価値観が失敗の対処行動に与える影響-失敗体験の重大性と領域を考えて-</t>
         </is>
@@ -827,33 +838,34 @@
           <t>釆原 周弥</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>Priority-neutral matchingsの集合の格子構造に関する研究</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; マッチング理論・ゲーム理論</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -864,7 +876,7 @@
 協力ゲーム・非協力ゲーム</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Priority-neutral matchingsの集合の格子構造に関する研究</t>
         </is>
@@ -876,33 +888,34 @@
           <t>金井 公亮</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>不確実性下の同質財割当における randomized uniform rule のパレート効率性について</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化 ; マッチング理論・ゲーム理論 ; オペレーションズリサーチ ; 機械学習</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>数理最適化
 組合せ最適化
@@ -921,7 +934,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>不確実性下の同質財割当における randomized uniform rule のパレート効率性について</t>
         </is>
@@ -933,33 +946,34 @@
           <t>原 笙太</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>都市特性・社会経済要因が外国人居住パターンに与える影響：東京23区の実証・シミュレーション分析</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>マルチエージェントシミュレーション</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
         <is>
           <t>マルチエージェントシミュレーション ; 都市・地域政策 ; GIS・空間分析 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>マルチエージェントシミュレーション
 都市・地域政策
@@ -979,7 +993,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>都市特性・社会経済要因が外国人居住パターンに与える影響：東京23区の実証・シミュレーション分析</t>
         </is>
@@ -991,33 +1005,34 @@
           <t>間嶋 大智</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>マルチエージェントシミュレーション&amp;最適化による間取り生成</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; マルチエージェントシミュレーション</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; マルチエージェントシミュレーション ; オペレーションズリサーチ ; 建築・空間設計</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>数理最適化
 組合せ最適化
@@ -1031,7 +1046,7 @@
 都市空間デザイン</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>マルチエージェントシミュレーション&amp;最適化による間取り生成</t>
         </is>
@@ -1043,33 +1058,34 @@
           <t>山田 幹大</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>eスポーツにおけるチームのプレイスタイル分析</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; スポーツデータ分析</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -1079,7 +1095,7 @@
 パフォーマンス分析</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>eスポーツにおけるチームのプレイスタイル分析</t>
         </is>
@@ -1091,33 +1107,34 @@
           <t>笹木 重聖</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>単位コイングラフにおける部分彩色の拡張</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>ネットワーク科学 ; グラフ理論</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>ネットワーク科学 ; グラフ理論 ; ネットワーク・グラフ理論</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>ネットワーク科学
 グラフ理論
@@ -1127,7 +1144,7 @@
 組合せ構造</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>単位コイングラフにおける部分彩色の拡張</t>
         </is>
@@ -1139,33 +1156,34 @@
           <t>井出 裕二</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>人口を考慮した均等輸送問題による道路ネットワークの連結性の定量化とその最適補強問題</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; ネットワーク科学 ; グラフ理論 ; 交通工学 ; 輸送最適化</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; ネットワーク科学 ; グラフ理論 ; 交通工学 ; 輸送最適化 ; 家族・人口政策 ; オペレーションズリサーチ ; 交通・モビリティ ; ネットワーク・グラフ理論</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>数理最適化
 組合せ最適化
@@ -1190,7 +1208,7 @@
 組合せ構造</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>人口を考慮した均等輸送問題による道路ネットワークの連結性の定量化とその最適補強問題</t>
         </is>
@@ -1202,33 +1220,34 @@
           <t>矢中 祥吾</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>消費電力と所要時間の不確実性を考慮した電動バスの運行計画最適化</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化 ; 交通工学 ; 輸送最適化 ; エネルギーシステム ; 運用最適化</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化 ; 交通工学 ; 輸送最適化 ; エネルギーシステム ; 運用最適化 ; オペレーションズリサーチ ; 交通・モビリティ ; 機械学習 ; 環境・エネルギー</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>数理最適化
 組合せ最適化
@@ -1254,7 +1273,7 @@
 持続可能性評価</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>消費電力と所要時間の不確実性を考慮した電動バスの運行計画最適化</t>
         </is>
@@ -1266,33 +1285,34 @@
           <t>片岡 弓澄</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>品質保証時間と工場間搬送を考慮した多目的マルチファクトリー・スケジューリング</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>数理最適化
 組合せ最適化
@@ -1300,7 +1320,7 @@
 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>品質保証時間と工場間搬送を考慮した多目的マルチファクトリー・スケジューリング</t>
         </is>
@@ -1312,33 +1332,34 @@
           <t>渡邊 悠義</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>自律性モデルに基づくゲーミフィケーションによる安全行動変容</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学 ; 意思決定分析</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
@@ -1349,7 +1370,7 @@
 意思決定支援</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>自律性モデルに基づくゲーミフィケーションによる安全行動変容</t>
         </is>
@@ -1361,33 +1382,34 @@
           <t>小澤 陽樹</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>確率的最適化による高次元交互作用スパースモデリング~Factorization Machines の発展形態</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化 ; データサイエンス ; 統計モデリング</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; 確率モデリング ; 確率最適化 ; データサイエンス ; 統計モデリング ; オペレーションズリサーチ ; 機械学習</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>数理最適化
 組合せ最適化
@@ -1403,7 +1425,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>確率的最適化による高次元交互作用スパースモデリング~Factorization Machines の発展形態</t>
         </is>
@@ -1415,33 +1437,34 @@
           <t>安田 朗</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>画像と生体計測情報に基づくアクティブラーニングと業務管理</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 機械学習 ; 画像・視覚情報処理 ; 医療・ヘルスデータ</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -1461,7 +1484,7 @@
 統計解析</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>画像と生体計測情報に基づくアクティブラーニングと業務管理</t>
         </is>
@@ -1473,33 +1496,34 @@
           <t>古山 雄晟</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>単独と集団を区別したライドシェアモデルにおけるゲーム理論的解析</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>ゲーム理論 ; マッチング理論</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>ゲーム理論 ; マッチング理論 ; マッチング理論・ゲーム理論 ; 交通・モビリティ</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>安定マッチング ; 資源配分 ; メカニズムデザイン ; 協力ゲーム・非協力ゲーム ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>ゲーム理論
 マッチング理論
@@ -1515,7 +1539,7 @@
 ネットワーク設計</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>単独と集団を区別したライドシェアモデルにおけるゲーム理論的解析</t>
         </is>
@@ -1527,33 +1551,34 @@
           <t>関田 千隼</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>異なる容量を持つ複数システムの負荷分散</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; オペレーションズリサーチ</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -1563,7 +1588,7 @@
 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>異なる容量を持つ複数システムの負荷分散</t>
         </is>
@@ -1575,33 +1600,34 @@
           <t>位曼曼</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>歩車共存空間における歩行者の移動モデルの構築</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; GIS・空間分析 ; 交通・モビリティ ; 建築・空間設計</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -1622,7 +1648,7 @@
 都市空間デザイン</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>歩車共存空間における歩行者の移動モデルの構築</t>
         </is>
@@ -1634,33 +1660,34 @@
           <t>三輪 珠嶺</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>骨格に基づく行動認識における関節角の導入</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学 ; 機械学習 ; 画像・視覚情報処理</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
@@ -1675,7 +1702,7 @@
 マルチモーダル解析</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>骨格に基づく行動認識における関節角の導入</t>
         </is>
@@ -1687,33 +1714,34 @@
           <t>加口 貴美子</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>日本における男女の賃金格差の推移</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 労働経済・就職マッチング ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -1729,7 +1757,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>日本における男女の賃金格差の推移</t>
         </is>
@@ -1741,33 +1769,34 @@
           <t>田之口 輝毅</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>SNS上のESGセンチメント</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 保険・金融行動 ; 機械学習 ; テキスト分析・NLP</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -1787,7 +1816,7 @@
 社会データ分析</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>SNS上のESGセンチメント</t>
         </is>
@@ -1799,33 +1828,34 @@
           <t>笹井 大</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>ESG関連インデックスと株式市場</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>経済モデリング ; 意思決定分析 ; 保険・金融行動 ; 機械学習</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>経済モデリング
 意思決定分析
@@ -1844,7 +1874,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>ESG関連インデックスと株式市場</t>
         </is>
@@ -1856,33 +1886,34 @@
           <t>水越 知弘</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>介護が労働に与える影響</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 労働経済・就職マッチング ; 社会政策・福祉 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -1903,7 +1934,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>介護が労働に与える影響</t>
         </is>
@@ -1915,33 +1946,34 @@
           <t>鈴木 優梨歌</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>複数工場間の経路最適化を含む多目的マルチファクトリー・スケジューリング</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>数理最適化
 組合せ最適化
@@ -1949,7 +1981,7 @@
 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>複数工場間の経路最適化を含む多目的マルチファクトリー・スケジューリング</t>
         </is>
@@ -1961,33 +1993,34 @@
           <t>永井 康友</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>品質検査レイヤーを横断した異常原因探索～画像マルチモーダルアプローチ</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 機械学習 ; 画像・視覚情報処理</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2002,7 +2035,7 @@
 マルチモーダル解析</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>品質検査レイヤーを横断した異常原因探索～画像マルチモーダルアプローチ</t>
         </is>
@@ -2014,33 +2047,34 @@
           <t>戴 家成</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>機械サーバと人間サーバが混在するサービスシステムの性能解析</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; サービス・待ち行列</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>待ち行列理論 ; サービス工学 ; システム性能評価</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2050,7 +2084,7 @@
 システム性能評価</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>機械サーバと人間サーバが混在するサービスシステムの性能解析</t>
         </is>
@@ -2062,33 +2096,34 @@
           <t>神野 大地</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>東京証券取引所によるPBR改善要請の影響は企業特性によって異なるか？</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 保険・金融行動 ; 都市・地域政策 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2109,7 +2144,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>東京証券取引所によるPBR改善要請の影響は企業特性によって異なるか？</t>
         </is>
@@ -2121,33 +2156,34 @@
           <t>LU SICHEN</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>四川大震災についての地元住民の記憶とその変容—汶川県映秀鎮と北川県を比較して—</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 災害・防災研究</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>災害社会学 ; 防災政策 ; リスク評価</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2157,7 +2193,7 @@
 リスク評価</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>四川大震災についての地元住民の記憶とその変容—汶川県映秀鎮と北川県を比較して—</t>
         </is>
@@ -2169,33 +2205,34 @@
           <t>石川 夏帆</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>多様な主体が関わる出産祝いによる産後家庭アウトリーチの実態と課題－横浜市戸塚区の認定NPO法人こまちぷらすのウェルカムベビープロジェクトに着目して－</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 家族・人口政策 ; 社会政策・福祉</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2211,7 +2248,7 @@
 非営利組織論</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>多様な主体が関わる出産祝いによる産後家庭アウトリーチの実態と課題－横浜市戸塚区の認定NPO法人こまちぷらすのウェルカムベビープロジェクトに着目して－</t>
         </is>
@@ -2223,33 +2260,34 @@
           <t>鳩貝 優太</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>カフェ型居場所の開設・運営プロセスにおける障壁と支援に関する研究－認定NPO法人こまちぷらすの講座に着目して－</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 社会政策・福祉</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>社会福祉政策 ; 地域福祉 ; 子育て支援 ; 非営利組織論</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2260,7 +2298,7 @@
 非営利組織論</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>カフェ型居場所の開設・運営プロセスにおける障壁と支援に関する研究－認定NPO法人こまちぷらすの講座に着目して－</t>
         </is>
@@ -2272,33 +2310,34 @@
           <t>畑 颯汰</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>斜面住宅地の存続可能性に関する研究 －段差解消のための共有財の維持管理に着目して－</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 建築・空間設計</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2314,7 +2353,7 @@
 都市空間デザイン</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>斜面住宅地の存続可能性に関する研究 －段差解消のための共有財の維持管理に着目して－</t>
         </is>
@@ -2326,33 +2365,34 @@
           <t>石田 悠人</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>公園の農的利用の効果と課題に関する研究</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2368,7 +2408,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>公園の農的利用の効果と課題に関する研究</t>
         </is>
@@ -2380,33 +2420,34 @@
           <t>高橋 慧</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>地方自治体における統計的因果推論に基づく政策分析の適用方法に関する研究</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2422,7 +2463,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>地方自治体における統計的因果推論に基づく政策分析の適用方法に関する研究</t>
         </is>
@@ -2434,33 +2475,34 @@
           <t>酒井 佑</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>地域外の人材を対象とした逆指名による創業支援制度の運用実態と他地域展開の可能性に関する研究</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2471,7 +2513,7 @@
 公共政策評価</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>地域外の人材を対象とした逆指名による創業支援制度の運用実態と他地域展開の可能性に関する研究</t>
         </is>
@@ -2483,33 +2525,34 @@
           <t>佐藤 佳乃</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>地籍調査の進捗に関する地理空間分析</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2530,7 +2573,7 @@
 都市空間デザイン</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>地籍調査の進捗に関する地理空間分析</t>
         </is>
@@ -2542,33 +2585,34 @@
           <t>早坂 遼</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>羽田空港新飛行経路の運用開始が東京都心の不動産価値に与えた影響に関する計量分析</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; GIS・空間分析 ; 交通・モビリティ ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2594,7 +2638,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>羽田空港新飛行経路の運用開始が東京都心の不動産価値に与えた影響に関する計量分析</t>
         </is>
@@ -2606,33 +2650,34 @@
           <t>釜谷 紘生</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>マニラ都市圏における洪水リスクが不動産価格に与える影響の分析</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; GIS・空間分析 ; 災害・防災研究 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 災害社会学 ; 防災政策 ; リスク評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2657,7 +2702,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>マニラ都市圏における洪水リスクが不動産価格に与える影響の分析</t>
         </is>
@@ -2669,33 +2714,34 @@
           <t>市川 はるひ</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>冒険遊び場における犯罪被害と運営者の対応の実態解明</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 災害・防災研究</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>災害社会学 ; 防災政策 ; リスク評価</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2705,7 +2751,7 @@
 リスク評価</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>冒険遊び場における犯罪被害と運営者の対応の実態解明</t>
         </is>
@@ -2717,33 +2763,34 @@
           <t>舩戸 祐汰</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>屋外着座空間への評価と独り好き志向性との関係</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; GIS・空間分析 ; 建築・空間設計</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2759,7 +2806,7 @@
 都市空間デザイン</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>屋外着座空間への評価と独り好き志向性との関係</t>
         </is>
@@ -2771,33 +2818,34 @@
           <t>廣田 華</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>農村舞台の現状とその保全—ハード・ソフトの両面に着目して—</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 建築・空間設計</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2808,7 +2856,7 @@
 都市空間デザイン</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>農村舞台の現状とその保全—ハード・ソフトの両面に着目して—</t>
         </is>
@@ -2820,33 +2868,34 @@
           <t>陳 泓儒</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>ディープラーニングに基づく武漢の都市イメージの空間構造と都市計画実施に関する研究</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; GIS・空間分析 ; 建築・空間設計</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2867,7 +2916,7 @@
 都市空間デザイン</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>ディープラーニングに基づく武漢の都市イメージの空間構造と都市計画実施に関する研究</t>
         </is>
@@ -2879,33 +2928,34 @@
           <t>坂本 怜奈</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>地域ネットワークにおける中間支援組織の役割とマネジメントシステムの構築に関する考察</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>ネットワーク科学 ; グラフ理論</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
         <is>
           <t>ネットワーク科学 ; グラフ理論 ; 都市・地域政策 ; ネットワーク・グラフ理論</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>ネットワーク科学
 グラフ理論
@@ -2920,7 +2970,7 @@
 組合せ構造</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>地域ネットワークにおける中間支援組織の役割とマネジメントシステムの構築に関する考察</t>
         </is>
@@ -2932,33 +2982,34 @@
           <t>佐々木 智哉</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>都市再生緊急整備地域における都市再生の政策効果の検証ー地方中核都市の事例を対象として</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -2974,7 +3025,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>都市再生緊急整備地域における都市再生の政策効果の検証ー地方中核都市の事例を対象として</t>
         </is>
@@ -2986,33 +3037,34 @@
           <t>髙野 駿</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>観光都市におけるオーバーツーリズムの対策やそれに伴う効果と課題について</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 政策評価・計量分析 ; 観光・マーケティング</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -3033,7 +3085,7 @@
 需要予測</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>観光都市におけるオーバーツーリズムの対策やそれに伴う効果と課題について</t>
         </is>
@@ -3045,33 +3097,34 @@
           <t>高橋 梨沙子</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>観光地における駅舎建築に関する研究</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 建築・空間設計 ; 観光・マーケティング</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -3087,7 +3140,7 @@
 需要予測</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>観光地における駅舎建築に関する研究</t>
         </is>
@@ -3099,33 +3152,34 @@
           <t>小松 諒治</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>地域公共交通サービス変化時の活動機会変化の計測に関する研究</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>交通工学 ; 輸送最適化</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
         <is>
           <t>交通工学 ; 輸送最適化 ; 都市・地域政策 ; オペレーションズリサーチ ; 交通・モビリティ</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>交通工学
 輸送最適化
@@ -3144,7 +3198,7 @@
 ネットワーク設計</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>地域公共交通サービス変化時の活動機会変化の計測に関する研究</t>
         </is>
@@ -3156,33 +3210,34 @@
           <t>佐光 未帆</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>大学敷地内における大学生の犯罪被害の実態と報告行動の解明</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学 ; 災害・防災研究</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>災害社会学 ; 防災政策 ; リスク評価</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
@@ -3192,7 +3247,7 @@
 リスク評価</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>大学敷地内における大学生の犯罪被害の実態と報告行動の解明</t>
         </is>
@@ -3204,33 +3259,34 @@
           <t>Tang Xinyu</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>職住近接と生活域の拡がりとの関連：GPSデータを用いた検討</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>データサイエンス ; 統計モデリング</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
         <is>
           <t>データサイエンス ; 統計モデリング ; 機械学習</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>データサイエンス
 統計モデリング
@@ -3240,7 +3296,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>職住近接と生活域の拡がりとの関連：GPSデータを用いた検討</t>
         </is>
@@ -3252,33 +3308,34 @@
           <t>田上 朋樹</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>人口再配分による食料需給バランス改善への試案 ー「地域で食料が自給できる国土」への視座－</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 家族・人口政策 ; 都市・地域政策</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -3294,7 +3351,7 @@
 公共政策評価</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>人口再配分による食料需給バランス改善への試案 ー「地域で食料が自給できる国土」への視座－</t>
         </is>
@@ -3306,33 +3363,34 @@
           <t>矢橋 敦之</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>都市サービスの長期的な入れ替わりの実態 －2002年と2022年の２時点比較－</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -3343,7 +3401,7 @@
 公共政策評価</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>都市サービスの長期的な入れ替わりの実態 －2002年と2022年の２時点比較－</t>
         </is>
@@ -3355,39 +3413,40 @@
           <t>松浦 海斗</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>子どもの体験格差の全国横断的把握 ―学校外での生活行動に着目して－</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>子どもの体験格差の全国横断的把握 ―学校外での生活行動に着目して－</t>
         </is>
@@ -3399,33 +3458,34 @@
           <t>稲葉 翔太</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>シェアサイクル運営者の機会損失改善に向けた自転車再配置における調整台数の検討-茨城県つくば市を事例として-</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 交通・モビリティ</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -3436,7 +3496,7 @@
 ネットワーク設計</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>シェアサイクル運営者の機会損失改善に向けた自転車再配置における調整台数の検討-茨城県つくば市を事例として-</t>
         </is>
@@ -3448,39 +3508,40 @@
           <t>三重野 馨</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>アルジェリアにおけるフェルナン・プイヨンのツーリスト・コンプレックスに関する研究</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>アルジェリアにおけるフェルナン・プイヨンのツーリスト・コンプレックスに関する研究</t>
         </is>
@@ -3492,33 +3553,34 @@
           <t>犬竹 智哉</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
           <t>商用FCVの普及に向けた水素ステーション配置とCO2排出量の予測</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 交通・モビリティ ; 環境・エネルギー</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -3534,7 +3596,7 @@
 持続可能性評価</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>商用FCVの普及に向けた水素ステーション配置とCO2排出量の予測</t>
         </is>
@@ -3546,33 +3608,34 @@
           <t>日高 優一</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
           <t>基幹交通の組み合わせ利用を考慮した将来交通需要予測に関する研究</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>交通工学 ; 輸送最適化</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
         <is>
           <t>交通工学 ; 輸送最適化 ; オペレーションズリサーチ ; 交通・モビリティ ; 観光・マーケティング</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>交通工学
 輸送最適化
@@ -3591,7 +3654,7 @@
 需要予測</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>基幹交通の組み合わせ利用を考慮した将来交通需要予測に関する研究</t>
         </is>
@@ -3603,33 +3666,34 @@
           <t>鎌田 晴人</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>ETC2.0プローブデータを活用した旅行時間信頼性の時空間的評価</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>データサイエンス ; 統計モデリング</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
         <is>
           <t>データサイエンス ; 統計モデリング ; GIS・空間分析 ; 建築・空間設計 ; 機械学習</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>データサイエンス
 統計モデリング
@@ -3649,7 +3713,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>ETC2.0プローブデータを活用した旅行時間信頼性の時空間的評価</t>
         </is>
@@ -3661,33 +3725,34 @@
           <t>畑山 公希</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
           <t>自治体におけるグリーンインフラの計画的展開を阻害する要因についての研究</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 環境・エネルギー</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -3703,7 +3768,7 @@
 持続可能性評価</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>自治体におけるグリーンインフラの計画的展開を阻害する要因についての研究</t>
         </is>
@@ -3715,39 +3780,40 @@
           <t>張 宇星</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>清代における祭祀行宮の構成と変容—龍王廟を中心に—</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>清代における祭祀行宮の構成と変容—龍王廟を中心に—</t>
         </is>
@@ -3759,33 +3825,34 @@
           <t>森下 陽平</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
           <t>騒音問題と自己観の関係性：日本・カナダ比較研究</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 災害・防災研究</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>災害社会学 ; 防災政策 ; リスク評価</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -3795,7 +3862,7 @@
 リスク評価</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>騒音問題と自己観の関係性：日本・カナダ比較研究</t>
         </is>
@@ -3807,33 +3874,34 @@
           <t>平林 優希</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
           <t>環境配慮意識・行動の自他評価の特性と行動意図の関係</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
         <is>
           <t>行動科学 ; 行動経済学 ; 環境・エネルギー</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>行動科学
 行動経済学
@@ -3844,7 +3912,7 @@
 持続可能性評価</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>環境配慮意識・行動の自他評価の特性と行動意図の関係</t>
         </is>
@@ -3856,33 +3924,34 @@
           <t>中澤 光希</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>都市再生特別地区において多様化する域外貢献の実態と課題に関する研究</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -3893,7 +3962,7 @@
 公共政策評価</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>都市再生特別地区において多様化する域外貢献の実態と課題に関する研究</t>
         </is>
@@ -3905,33 +3974,34 @@
           <t>草田 弦喜</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>銀座ルールと比較した『日本橋らしさ』に関する研究-東京都日本橋地区を対象として-</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -3942,7 +4012,7 @@
 公共政策評価</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>銀座ルールと比較した『日本橋らしさ』に関する研究-東京都日本橋地区を対象として-</t>
         </is>
@@ -3954,33 +4024,34 @@
           <t>加藤 優弥</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>スタジアム・アリーナの多機能化に伴う公民連携によるエリアマネジメントに関する研究</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 建築・空間設計 ; スポーツデータ分析</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -3995,7 +4066,7 @@
 パフォーマンス分析</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>スタジアム・アリーナの多機能化に伴う公民連携によるエリアマネジメントに関する研究</t>
         </is>
@@ -4007,33 +4078,34 @@
           <t>水野 瑛介</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
           <t>メジャーリーグにおける統計的差別と選好的差別</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 意思決定分析</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4044,7 +4116,7 @@
 意思決定支援</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>メジャーリーグにおける統計的差別と選好的差別</t>
         </is>
@@ -4056,33 +4128,34 @@
           <t>山縣 力也</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>非罰則規制の犯罪波及効果：渋谷区の路上飲酒禁止条例を事例として</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4093,7 +4166,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>非罰則規制の犯罪波及効果：渋谷区の路上飲酒禁止条例を事例として</t>
         </is>
@@ -4105,33 +4178,34 @@
           <t>青木 日花</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
           <t>アメニティに着目した価値あるオフィスビルの要因分析と効果検証</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4142,7 +4216,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>アメニティに着目した価値あるオフィスビルの要因分析と効果検証</t>
         </is>
@@ -4154,33 +4228,34 @@
           <t>GAO WENWEN</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
           <t>グリーンビルディング認証がJ-REITのパフォーマンスに与える影響の実証分析</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 政策評価・計量分析 ; 環境・エネルギー</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4196,7 +4271,7 @@
 持続可能性評価</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>グリーンビルディング認証がJ-REITのパフォーマンスに与える影響の実証分析</t>
         </is>
@@ -4208,33 +4283,34 @@
           <t>平野 晴也</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
           <t>3次元地図更新のための衛星リモートセンシングによる地形計測手法の開発</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; GIS・空間分析 ; 画像・視覚情報処理</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>GIS ; 空間計量 ; 地理情報分析 ; 立地分析 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4250,7 +4326,7 @@
 マルチモーダル解析</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>3次元地図更新のための衛星リモートセンシングによる地形計測手法の開発</t>
         </is>
@@ -4262,33 +4338,34 @@
           <t>WEI MIAOHENG</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
           <t>往復移動と滞在行動を考慮したバス頻度問題</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>交通工学 ; 輸送最適化 ; 行動科学 ; 行動経済学</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
         <is>
           <t>交通工学 ; 輸送最適化 ; 行動科学 ; 行動経済学 ; オペレーションズリサーチ ; 交通・モビリティ</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>交通工学
 輸送最適化
@@ -4304,7 +4381,7 @@
 ネットワーク設計</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>往復移動と滞在行動を考慮したバス頻度問題</t>
         </is>
@@ -4316,33 +4393,34 @@
           <t>田村 侑介</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
           <t>共同住宅におけるEV充電器設置の意思決定メカニズムの解析</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>経済モデリング ; 意思決定分析</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
         <is>
           <t>経済モデリング ; 意思決定分析 ; 建築・空間設計 ; 機械学習</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 建築計画 ; 空間レイアウト生成 ; 居住空間設計 ; 都市空間デザイン ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>経済モデリング
 意思決定分析
@@ -4361,7 +4439,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>共同住宅におけるEV充電器設置の意思決定メカニズムの解析</t>
         </is>
@@ -4373,33 +4451,34 @@
           <t>山田 圭祐</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
           <t>ミクロ交通シミュレーション利用における機械学習モデルの有効性検討</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>交通工学 ; 輸送最適化 ; マルチエージェントシミュレーション ; データサイエンス ; 統計モデリング</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
         <is>
           <t>交通工学 ; 輸送最適化 ; マルチエージェントシミュレーション ; データサイエンス ; 統計モデリング ; オペレーションズリサーチ ; 交通・モビリティ ; 機械学習</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>交通工学
 輸送最適化
@@ -4420,7 +4499,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>ミクロ交通シミュレーション利用における機械学習モデルの有効性検討</t>
         </is>
@@ -4432,33 +4511,34 @@
           <t>平山 裕紀人</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
           <t>マクロ交通流理論に基づくグリッドロック現象の分析：タイ・バンコクを対象として</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>交通工学 ; 輸送最適化</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
         <is>
           <t>交通工学 ; 輸送最適化 ; オペレーションズリサーチ ; 交通・モビリティ</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>交通工学
 輸送最適化
@@ -4472,7 +4552,7 @@
 ネットワーク設計</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>マクロ交通流理論に基づくグリッドロック現象の分析：タイ・バンコクを対象として</t>
         </is>
@@ -4484,33 +4564,34 @@
           <t>桑原 慶太</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>データ同化手法を用いたネットワーク交通流モデルの精度改善及びパラメータ推定</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>ネットワーク科学 ; グラフ理論 ; 交通工学 ; 輸送最適化 ; データサイエンス ; 統計モデリング</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
         <is>
           <t>ネットワーク科学 ; グラフ理論 ; 交通工学 ; 輸送最適化 ; データサイエンス ; 統計モデリング ; オペレーションズリサーチ ; 交通・モビリティ ; 機械学習 ; ネットワーク・グラフ理論</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 交通工学 ; モビリティ設計 ; 交通需要分析 ; ネットワーク設計 ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>ネットワーク科学
 グラフ理論
@@ -4536,7 +4617,7 @@
 組合せ構造</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>データ同化手法を用いたネットワーク交通流モデルの精度改善及びパラメータ推定</t>
         </is>
@@ -4548,33 +4629,34 @@
           <t>徐 摯恒</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
           <t>高速鉄道の開通が都市経済に与える影響の分析</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 都市・地域政策 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4590,7 +4672,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>高速鉄道の開通が都市経済に与える影響の分析</t>
         </is>
@@ -4602,33 +4684,34 @@
           <t>松場 拓海</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
           <t>「認識人口」概念の提案とその実態―市町村に対するポジティブ／ネガティブイメージの分析から－</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 家族・人口政策 ; 画像・視覚情報処理</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>家族の経済学 ; 少子化対策 ; 人口政策 ; 家計意思決定 ; コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4644,7 +4727,7 @@
 マルチモーダル解析</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>「認識人口」概念の提案とその実態―市町村に対するポジティブ／ネガティブイメージの分析から－</t>
         </is>
@@ -4656,33 +4739,34 @@
           <t>馬場 理彰</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>プロサッカーチームのリーグ昇降格が街並みに与える影響</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; スポーツデータ分析 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>スポーツアナリティクス ; 戦術分析 ; パフォーマンス分析 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4697,7 +4781,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>プロサッカーチームのリーグ昇降格が街並みに与える影響</t>
         </is>
@@ -4709,33 +4793,34 @@
           <t>佐々木 智哉</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
           <t>コロナ禍以降のバイク需要の持続的拡大の要因：経験財理論に基づく考察</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 観光・マーケティング</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4746,7 +4831,7 @@
 需要予測</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>コロナ禍以降のバイク需要の持続的拡大の要因：経験財理論に基づく考察</t>
         </is>
@@ -4758,33 +4843,34 @@
           <t>網野 景介</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
           <t>M-1グランプリのシグナリング効果：動画再生数への影響</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4795,7 +4881,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>M-1グランプリのシグナリング効果：動画再生数への影響</t>
         </is>
@@ -4807,33 +4893,34 @@
           <t>神尾 瑞貴</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
           <t>花粉が経済活動に与える影響</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 政策評価・計量分析</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4844,7 +4931,7 @@
 実証分析</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>花粉が経済活動に与える影響</t>
         </is>
@@ -4856,33 +4943,34 @@
           <t>柳 千宙</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>MPPS</t>
-        </is>
-      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>分布北限域における南方系海洋生物の北上とその認識</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
         <is>
           <t>データ分析 ; 社会システム分析 ; 画像・視覚情報処理</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>コンピュータビジョン ; 画像認識 ; 行動認識 ; マルチモーダル解析</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>データ分析
 社会システム分析
@@ -4893,7 +4981,7 @@
 マルチモーダル解析</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>分布北限域における南方系海洋生物の北上とその認識</t>
         </is>
@@ -4910,7 +4998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4921,40 +5009,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>student_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>group</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>overview_field</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>research_content</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>research_field</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>detailed_research_field</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>field_text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>content_text</t>
         </is>
@@ -4966,37 +5059,38 @@
           <t>益子颯太</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>摘要欄情報を用いた仕訳データの異常検知モデルの開発</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>会計</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>摘要テキストを特徴量化し異常検知精度を向上</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>会計データ分析 ; 異常検知 ; NLP ; 機械学習 ; 会計・ファイナンス ; テキスト分析・NLP</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>会計
 会計データ分析
@@ -5017,7 +5111,7 @@
 社会データ分析</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>摘要欄情報を用いた仕訳データの異常検知モデルの開発
 摘要テキストを特徴量化し異常検知精度を向上</t>
@@ -5030,37 +5124,38 @@
           <t>加田昌杜</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>筑波大学学年歴の曜日変更最小化</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>数理最適化</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>曜日変更最小化による学年歴作成の自動化</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>スケジューリング ; 数理最適化 ; オペレーションズリサーチ</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>数理最適化
 スケジューリング
@@ -5069,7 +5164,7 @@
 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>筑波大学学年歴の曜日変更最小化
 曜日変更最小化による学年歴作成の自動化</t>
@@ -5082,33 +5177,34 @@
           <t>吉田響</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>中規模学会における発表スケジュール作成モデル</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>スケジューリング</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>スケジューリング ; オペレーションズリサーチ</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>スケジューリング
 オペレーションズリサーチ
@@ -5117,7 +5213,7 @@
 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>中規模学会における発表スケジュール作成モデル</t>
         </is>
@@ -5129,37 +5225,38 @@
           <t>佐川翼</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>多段階モデルを用いた修士論文発表会スケジューリングシステムの開発</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>スケジューリング</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>多段階最適化モデルによる発表会スケジューリング</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>スケジューリング ; 数理最適化 ; オペレーションズリサーチ</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>スケジューリング
 数理最適化
@@ -5168,7 +5265,7 @@
 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>多段階モデルを用いた修士論文発表会スケジューリングシステムの開発
 多段階最適化モデルによる発表会スケジューリング</t>
@@ -5181,37 +5278,38 @@
           <t>出口達也</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>日本の慢性腎臓病進行症例患者における地域のソーシャルキャピタルが腎機能低下に及ぼす影響の分析</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>データ解析</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Cox回帰により地域要因と腎機能低下の関係を分析</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>医療データ分析 ; 統計解析 ; 都市・地域政策 ; 政策評価・計量分析 ; 医療・ヘルスデータ</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>データ解析
 医療データ分析
@@ -5231,7 +5329,7 @@
 ヘルスデータサイエンス</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>日本の慢性腎臓病進行症例患者における地域のソーシャルキャピタルが腎機能低下に及ぼす影響の分析
 Cox回帰により地域要因と腎機能低下の関係を分析</t>
@@ -5244,37 +5342,38 @@
           <t>川井貫太朗</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>SNSデータを用いた日本の空気感と単語ネットワーク</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>テキストマイニング</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>単語ネットワークにより集団感情を分析</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>テキスト分析 ; 感情分析 ; ネットワーク・グラフ理論 ; テキスト分析・NLP</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>テキストマイニング
 テキスト分析
@@ -5289,7 +5388,7 @@
 社会データ分析</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SNSデータを用いた日本の空気感と単語ネットワーク
 単語ネットワークにより集団感情を分析</t>
@@ -5302,37 +5401,38 @@
           <t>但木陸</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>大学入試業務の人員配置最適化における暗黙知制約の検知と数理モデルの改良</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>数理最適化</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>機械学習で制約抽出し最適化に組み込む</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>数理最適化 ; 機械学習 ; オペレーションズリサーチ</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>数理最適化
 機械学習
@@ -5344,7 +5444,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>大学入試業務の人員配置最適化における暗黙知制約の検知と数理モデルの改良
 機械学習で制約抽出し最適化に組み込む</t>
@@ -5357,37 +5457,38 @@
           <t>中山友琉</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>データ分散状況を想定したプライバシー保護ハザード比推定手法の提案</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>データ解析</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>分散環境での統計推定手法の開発</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>統計解析 ; 医療データ ; 医療・ヘルスデータ ; 環境・エネルギー</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析 ; 環境政策 ; エネルギーシステム ; 脱炭素分析 ; 持続可能性評価</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>データ解析
 統計解析
@@ -5403,7 +5504,7 @@
 持続可能性評価</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>データ分散状況を想定したプライバシー保護ハザード比推定手法の提案
 分散環境での統計推定手法の開発</t>
@@ -5416,37 +5517,38 @@
           <t>中本武志</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>パートタイム労働者を主力とするサービス業におけるシフトスケジューリング</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>スケジューリング</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>需要と公平性を考慮した勤務スケジュール作成</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>スケジューリング ; 数理最適化 ; 労働経済・就職マッチング ; オペレーションズリサーチ ; 観光・マーケティング</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>労働経済 ; 人的資本 ; 就職マッチング ; 採用市場設計 ; 数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>スケジューリング
 数理最適化
@@ -5465,7 +5567,7 @@
 需要予測</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>パートタイム労働者を主力とするサービス業におけるシフトスケジューリング
 需要と公平性を考慮した勤務スケジュール作成</t>
@@ -5478,37 +5580,38 @@
           <t>長谷川弘貴</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>生体データにもとづくサービスデータ解析手法の提案</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>データ解析</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>高次元データ解析手法による評価モデル構築</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>ビッグデータ解析 ; 生体情報 ; 医療・ヘルスデータ</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>データ解析
 ビッグデータ解析
@@ -5520,7 +5623,7 @@
 統計解析</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>生体データにもとづくサービスデータ解析手法の提案
 高次元データ解析手法による評価モデル構築</t>
@@ -5533,37 +5636,38 @@
           <t>堤敬信</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>待ち行列モデルを用いた機械学習システムの性能分析</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>待ち行列理論</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>待ち行列モデルで性能と効率を分析</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>待ち行列理論 ; 機械学習 ; サービス・待ち行列</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習 ; 待ち行列理論 ; サービス工学 ; システム性能評価</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>待ち行列理論
 機械学習
@@ -5575,7 +5679,7 @@
 システム性能評価</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>待ち行列モデルを用いた機械学習システムの性能分析
 待ち行列モデルで性能と効率を分析</t>
@@ -5588,37 +5692,38 @@
           <t>飯田真実</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>HPVワクチン接種に対する意見の変遷とその要因</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>テキストマイニング</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>SNSデータから意見変遷の要因分析</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>テキスト分析 ; 社会データ ; テキスト分析・NLP ; 医療・ヘルスデータ</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析 ; 医療データ分析 ; 生体情報解析 ; ヘルスデータサイエンス ; 統計解析</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>テキストマイニング
 テキスト分析
@@ -5634,7 +5739,7 @@
 統計解析</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>HPVワクチン接種に対する意見の変遷とその要因
 SNSデータから意見変遷の要因分析</t>
@@ -5647,37 +5752,38 @@
           <t>冨樫歩大</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>大規模言語モデルを用いた事業性評価シートのテキスト分析</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>アカウンティングインフォマティクス</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>LLMでテキスト分析し融資支援</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>自然言語処理 ; 金融データ ; 保険・金融行動 ; テキスト分析・NLP</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>アカウンティングインフォマティクス
 自然言語処理
@@ -5693,7 +5799,7 @@
 社会データ分析</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>大規模言語モデルを用いた事業性評価シートのテキスト分析
 LLMでテキスト分析し融資支援</t>
@@ -5706,37 +5812,38 @@
           <t>平井佑樹</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>仕訳データにもとづく利速測定の研究</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>会計</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>仕訳データから利速を測定</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>会計データ分析 ; 時系列 ; 会計・ファイナンス</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>会計
 会計データ分析
@@ -5747,7 +5854,7 @@
 会計情報システム</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>仕訳データにもとづく利速測定の研究
 仕訳データから利速を測定</t>
@@ -5760,37 +5867,38 @@
           <t>李宗晟</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>光ネットワークにおける予約のある資源割り当ての提案</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>数理最適化</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>予約付きモデルで断片化を抑制</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>ネットワーク最適化 ; オペレーションズリサーチ ; ネットワーク・グラフ理論</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; グラフ理論 ; 離散数学 ; ネットワーク最適化 ; 組合せ構造</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>数理最適化
 ネットワーク最適化
@@ -5803,7 +5911,7 @@
 組合せ構造</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>光ネットワークにおける予約のある資源割り当ての提案
 予約付きモデルで断片化を抑制</t>
@@ -5816,37 +5924,38 @@
           <t>鈴木颯斗</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>クーポン配布における分類モデルの負例抽出</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>サービス評価</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>負例抽出アルゴリズムで推薦精度向上</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>機械学習 ; 推薦システム</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>機械学習 ; 統計的学習 ; 予測モデリング ; 表現学習</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>サービス評価
 機械学習
@@ -5856,7 +5965,7 @@
 表現学習</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>クーポン配布における分類モデルの負例抽出
 負例抽出アルゴリズムで推薦精度向上</t>
@@ -5869,37 +5978,38 @@
           <t>崔涵喬</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>クラスター分析を用いた観光客のセグメンテーションとマーケティングへの応用可能性に関する研究</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>クラスタリング</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>観光客クラスタリング分析</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>クラスタリング ; 観光データ ; 観光・マーケティング</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>観光データ分析 ; マーケティング分析 ; クラスタリング ; 需要予測</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>クラスタリング
 観光データ
@@ -5909,7 +6019,7 @@
 需要予測</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>クラスター分析を用いた観光客のセグメンテーションとマーケティングへの応用可能性に関する研究
 観光客クラスタリング分析</t>
@@ -5922,37 +6032,38 @@
           <t>澤口瑛都</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>列生成法を軸としたバス運行業務の仕業編成</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>数理最適化</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>列生成法による運行スケジュール最適化</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>数理最適化 ; スケジューリング ; オペレーションズリサーチ</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>数理最適化
 スケジューリング
@@ -5961,7 +6072,7 @@
 計画・スケジューリング</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>列生成法を軸としたバス運行業務の仕業編成
 列生成法による運行スケジュール最適化</t>
@@ -5974,37 +6085,38 @@
           <t>齋藤彩</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>pLSAによる潜在クラス間の遷移予想と効果検証</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>データ解析</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>pLSAで行動変容支援分析</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>確率モデル ; テキスト解析 ; 意思決定分析 ; 政策評価・計量分析 ; テキスト分析・NLP</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>行動意思決定 ; 実験・行動分析 ; ナッジ ; 意思決定支援 ; 政策評価 ; 計量経済学 ; 統計的因果推論 ; 実証分析 ; テキストマイニング ; 自然言語処理 ; 感情分析 ; 社会データ分析</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>データ解析
 確率モデル
@@ -6026,7 +6138,7 @@
 社会データ分析</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>pLSAによる潜在クラス間の遷移予想と効果検証
 pLSAで行動変容支援分析</t>
@@ -6039,33 +6151,34 @@
           <t>髙橋優介</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>実データを用いた平常時の収益性と災害時の孤立リスクを考慮したドローン配送基地の施設立地最適化</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>シミュレーション</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>シミュレーション ; オペレーションズリサーチ ; 災害・防災研究</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>数理最適化 ; 組合せ最適化 ; オペレーションズリサーチ ; 計画・スケジューリング ; 災害社会学 ; 防災政策 ; リスク評価</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>シミュレーション
 オペレーションズリサーチ
@@ -6078,7 +6191,7 @@
 リスク評価</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>実データを用いた平常時の収益性と災害時の孤立リスクを考慮したドローン配送基地の施設立地最適化</t>
         </is>
@@ -6090,37 +6203,38 @@
           <t>寺田海渡</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
         <is>
           <t>MSE</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>地域金融機関の預貸金データを用いた中小企業会計品質指標の提案</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>会計</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>預貸金データから会計品質を定量化</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>金融データ分析 ; 会計 ; 保険・金融行動 ; 都市・地域政策 ; 会計・ファイナンス</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>行動ファイナンス ; 金融市場分析 ; ESG投資 ; 企業財務 ; 都市経済 ; 地域政策 ; 土地利用 ; 公共政策評価 ; 会計データ分析 ; 財務会計 ; 管理会計 ; 会計情報システム</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>会計
 金融データ分析
@@ -6141,7 +6255,7 @@
 会計情報システム</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>地域金融機関の預貸金データを用いた中小企業会計品質指標の提案
 預貸金データから会計品質を定量化</t>

--- a/generated/students_enriched.xlsx
+++ b/generated/students_enriched.xlsx
@@ -487,7 +487,11 @@
           <t>中島 元毅</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>202420453</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -545,7 +549,11 @@
           <t>荒金 志紀</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>202420409</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -608,7 +616,11 @@
           <t>小峯 拓也</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>202420429</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -666,7 +678,11 @@
           <t>貫井 虹希</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>202420454</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -728,7 +744,11 @@
           <t>安達 未晴</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>202420407</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -783,7 +803,11 @@
           <t>YANG LUXI</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>202420493</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -838,7 +862,11 @@
           <t>釆原 周弥</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>202420416</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -888,7 +916,11 @@
           <t>金井 公亮</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>202420420</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -946,7 +978,11 @@
           <t>原 笙太</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>202420460</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1005,7 +1041,11 @@
           <t>間嶋 大智</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>202420467</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1058,7 +1098,11 @@
           <t>山田 幹大</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>202420484</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1107,7 +1151,11 @@
           <t>笹木 重聖</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>202420434</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1156,7 +1204,11 @@
           <t>井出 裕二</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>202420412</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1220,7 +1272,11 @@
           <t>矢中 祥吾</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>202420478</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1285,7 +1341,11 @@
           <t>片岡 弓澄</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>202320421</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1332,7 +1392,11 @@
           <t>渡邊 悠義</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>202420485</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1382,7 +1446,11 @@
           <t>小澤 陽樹</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>202420417</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1437,7 +1505,11 @@
           <t>安田 朗</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>202420477</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1496,7 +1568,11 @@
           <t>古山 雄晟</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>202420430</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1551,7 +1627,11 @@
           <t>関田 千隼</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>202420441</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1600,7 +1680,11 @@
           <t>位曼曼</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>202420487</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1660,7 +1744,11 @@
           <t>三輪 珠嶺</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>202420473</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1714,7 +1802,11 @@
           <t>加口 貴美子</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>202420418</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1769,7 +1861,11 @@
           <t>田之口 輝毅</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>202420447</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1828,7 +1924,11 @@
           <t>笹井 大</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>202420433</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1886,7 +1986,11 @@
           <t>水越 知弘</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>202420471</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1946,7 +2050,11 @@
           <t>鈴木 優梨歌</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>202420439</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -1993,7 +2101,11 @@
           <t>永井 康友</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>202420451</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2047,7 +2159,11 @@
           <t>戴 家成</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>202420442</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2096,7 +2212,11 @@
           <t>神野 大地</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>202420427</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2156,7 +2276,11 @@
           <t>LU SICHEN</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>202420494</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2205,7 +2329,11 @@
           <t>石川 夏帆</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>202420410</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2260,7 +2388,11 @@
           <t>鳩貝 優太</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>202420458</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2310,7 +2442,11 @@
           <t>畑 颯汰</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>202420456</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2365,7 +2501,11 @@
           <t>石田 悠人</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>202420411</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2420,7 +2560,11 @@
           <t>高橋 慧</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>202420444</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2475,7 +2619,11 @@
           <t>酒井 佑</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>202420431</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2525,7 +2673,11 @@
           <t>佐藤 佳乃</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>202420437</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2585,7 +2737,11 @@
           <t>早坂 遼</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>202420547</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2650,7 +2806,11 @@
           <t>釜谷 紘生</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>202420422</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2714,7 +2874,11 @@
           <t>市川 はるひ</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>202420455</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2763,7 +2927,11 @@
           <t>舩戸 祐汰</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>202420466</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2818,7 +2986,11 @@
           <t>廣田 華</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>202420465</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2868,7 +3040,11 @@
           <t>陳 泓儒</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>202420492</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2928,7 +3104,11 @@
           <t>坂本 怜奈</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>202420432</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -2982,7 +3162,11 @@
           <t>佐々木 智哉</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>202420435</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3037,7 +3221,11 @@
           <t>髙野 駿</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>202420443</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3097,7 +3285,11 @@
           <t>高橋 梨沙子</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>202420445</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3152,7 +3344,11 @@
           <t>小松 諒治</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>202420428</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3210,7 +3406,11 @@
           <t>佐光 未帆</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>202420438</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3259,7 +3459,11 @@
           <t>Tang Xinyu</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>202420490</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3308,7 +3512,11 @@
           <t>田上 朋樹</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>202420446</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3363,7 +3571,11 @@
           <t>矢橋 敦之</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>202420480</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3413,7 +3625,11 @@
           <t>松浦 海斗</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>202420468</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3458,7 +3674,11 @@
           <t>稲葉 翔太</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>202420413</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3508,7 +3728,11 @@
           <t>三重野 馨</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>202420470</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3553,7 +3777,11 @@
           <t>犬竹 智哉</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>202420414</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3608,7 +3836,11 @@
           <t>日高 優一</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>202420461</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3666,7 +3898,11 @@
           <t>鎌田 晴人</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>202420421</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3725,7 +3961,11 @@
           <t>畑山 公希</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>202420457</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3780,7 +4020,11 @@
           <t>張 宇星</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>202420491</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3825,7 +4069,11 @@
           <t>森下 陽平</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>202420474</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3874,7 +4122,11 @@
           <t>平林 優希</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>202420463</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3924,7 +4176,11 @@
           <t>中澤 光希</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>202420452</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -3974,7 +4230,11 @@
           <t>草田 弦喜</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>202420424</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4024,7 +4284,11 @@
           <t>加藤 優弥</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>202420419</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4078,7 +4342,11 @@
           <t>水野 瑛介</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>202420472</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4128,7 +4396,11 @@
           <t>山縣 力也</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>202420481</t>
+        </is>
+      </c>
       <c r="C69" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4178,7 +4450,11 @@
           <t>青木 日花</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>202420406</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4228,7 +4504,11 @@
           <t>GAO WENWEN</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>202420488</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4283,7 +4563,11 @@
           <t>平野 晴也</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>202420462</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4338,7 +4622,11 @@
           <t>WEI MIAOHENG</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>202420486</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4393,7 +4681,11 @@
           <t>田村 侑介</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>202420449</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4451,7 +4743,11 @@
           <t>山田 圭祐</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>202420483</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4511,7 +4807,11 @@
           <t>平山 裕紀人</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>202420464</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4564,7 +4864,11 @@
           <t>桑原 慶太</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>202420426</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4629,7 +4933,11 @@
           <t>徐 摯恒</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>202420489</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4684,7 +4992,11 @@
           <t>松場 拓海</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>202420469</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4739,7 +5051,11 @@
           <t>馬場 理彰</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>202420459</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4793,7 +5109,11 @@
           <t>佐々木 智哉</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>202420436</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4843,7 +5163,11 @@
           <t>網野 景介</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>202420408</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4893,7 +5217,11 @@
           <t>神尾 瑞貴</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>202420423</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>MPPS</t>
@@ -4943,7 +5271,11 @@
           <t>柳 千宙</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>202420479</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>MPPS</t>
